--- a/owp/owp-2109-live/cortex output files/OWP_2109_JCR_Cortex_v2.xlsx
+++ b/owp/owp-2109-live/cortex output files/OWP_2109_JCR_Cortex_v2.xlsx
@@ -36,12 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="379">
   <si>
     <t xml:space="preserve">OWP #2109 · Marysville Ph2</t>
   </si>
   <si>
-    <t xml:space="preserve">Intracorp · 246 units · CANCELLED</t>
+    <t xml:space="preserve">Intracorp · 246 units · ACTIVE · Roughin phase</t>
   </si>
   <si>
     <t xml:space="preserve">Forecast at Completion (Revised Basis)</t>
@@ -98,64 +98,418 @@
     <t xml:space="preserve">AR</t>
   </si>
   <si>
-    <t xml:space="preserve">Job Information</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job ID</t>
+    <t xml:space="preserve">PROJECT TEAM · KEY PLAYERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active project · Roughin phase. Team data from index.html PROJECT_TEAMS['2109'] + JDR + AP vendor concentration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Contractor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intracorp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP Roughin Foreman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garrett Wilson / Mitchell Gerard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP Estimator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeffrey S. Gerard / Jordan E. Gerard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP Signatory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Donelson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intracorp (owner-GC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEP / Plumbing Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franklin Engineering (per AP — $22.3k design fee)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marysville, WA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard (COI) — non-Wrap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE · Roughin phase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$3,700,937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Contract (rev)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$3,718,851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AR Billed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$3,570,012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retention Held</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$153,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Crew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 workers · 377 hrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOB #2109 · PROJECT INFORMATION &amp; KEY PLAYERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active project — Roughin phase. Team data sourced from index.html PROJECT_TEAMS['2109'] + Sage JDR identity block + AP vendor concentration analysis. GDrive folder not yet mounted; design-team contacts will be filled in once accessed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDENTITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job Number</t>
   </si>
   <si>
     <t xml:space="preserve">2109</t>
   </si>
   <si>
-    <t xml:space="preserve">Project name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marysville Ph2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">General contractor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intracorp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner</t>
+    <t xml:space="preserve">Job Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marysville Phase 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-family apartments — Phase 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permit</t>
   </si>
   <si>
     <t xml:space="preserve">TBD</t>
   </si>
   <si>
-    <t xml:space="preserve">Units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected completion</t>
+    <t xml:space="preserve">SCHEDULE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04 (active)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2028-02 (estimated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duration (est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedule Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apr 2026 → Feb 2028 (est. ~22 months) · Roughin in progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTRACT &amp; FINANCIALS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Change Orders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$17,914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AR Billed to Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Complete (billed/revised)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$2,683,501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Net Profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$886,511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retainage Held</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lien Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard subcontract — no priority docs filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warranty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard 1-yr plumbing (post-completion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract on File</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subcontract executed (revised contract $3,718,851)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCOPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plumbing Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Fixtures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD (fixture schedule not yet finalized in this dataset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixture Counts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECT TEAM — GENERAL CONTRACTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GC Project Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD (Intracorp) — primary contact pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GC Superintendent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GC Project Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECT TEAM — OWP STAFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP Trim Foreman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD (Trim phase not yet started — schedule Q3 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP Estimator (takeoff)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 workers · 377 hrs logged YTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECT TEAM — OWNER &amp; DEVELOPMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner of Record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECT TEAM — DESIGN</t>
   </si>
   <si>
     <t xml:space="preserve">Architect</t>
   </si>
   <si>
-    <t xml:space="preserve">MEP Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCELLED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JDR report date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apr 3, 2026</t>
+    <t xml:space="preserve">Structural Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Civil Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landscape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP VENDOR PROFILE (CURRENT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacific Plumbing Supply Co., LLC ($500,869 / 169 invoices / 46.7% of AP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total AP Spend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1,071,980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Vendors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 unique vendors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentration Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacific Plumbing 46.7% + Consolidated 28.5% + Rosen 9.7% = Top 3 dominate at 84.9% of AP. Standard for OWP active jobs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOCUMENT META (current)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay Apps (filed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracked in JDR (no separate filing log mounted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Executed COs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net +$17,914 booked (CO detail not yet itemized in this dataset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD — pending log extraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFIs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submittals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permit Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project is in active Roughin. Documents flow has begun but the GDrive folder for this job hasn't been wired to the dashboard yet — once mounted, the document counts will populate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA SOURCES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JDR PDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2109 Job Detail Report (Sage Timberline · Apr 3 2026 run)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsed Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2109_data.json (~3.7MB — full Sage extract)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dashboard Arrays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2109_dashboard_arrays.json (16 arrays sourced from index.html PROJECTS['2109'])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDrive Folder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not yet mounted to local environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDrive Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDrive folder not yet wired to local mount. Team data from index.html PROJECT_TEAMS['2109'] + JDR identity block.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RISK FLAGS / ACTIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New GC (Intracorp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP has no closed-job history with Intracorp. Pull AR aging report monthly. Watch payment cadence + change-order velocity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering overrun (601)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code 601 Engineering/Plans — actual $22,320 vs revised $5,850 (+281.5%). All booked to Franklin Engineering. Likely an early scope-add. Confirm CO coverage before trim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trim manpower forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roughin in progress. Trim phase typically starts at ~60% schedule completion. Coordinate with manpower allocation matrix for Q3 2026 crew availability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retention aging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$153,880 held · 4.3% of billed. Track release schedule once project nears closeout.</t>
   </si>
   <si>
     <t xml:space="preserve">Contract Summary</t>
@@ -209,9 +563,6 @@
     <t xml:space="preserve">Completed to Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Retention Held</t>
-  </si>
-  <si>
     <t xml:space="preserve">Previous Billed</t>
   </si>
   <si>
@@ -614,40 +965,112 @@
     <t xml:space="preserve">Hours per unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Predictive Signals (cancelled project)</t>
+    <t xml:space="preserve">Predictive Signals — Job #2109 (active · roughin)</t>
   </si>
   <si>
     <t xml:space="preserve">Signal</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering/Plans (601) CRITICAL overrun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠ WATCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual $22,320 vs revised $5,850 (+282%) — needs immediate attention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top vendor concentration (Pacific Plumbing Sup)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47% of AP ($500,869) — high, monitor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retention aging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✓ OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$153,880 held · 4.3% of billed · zero (cancelled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0% forecast margin — healthy</t>
+    <t xml:space="preserve">Current Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BVA Critical Flags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEALTHY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BVA Over Flags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change Order Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;25%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GC closed-job history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 jobs with Intracorp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WATCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+281.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;+50%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top-vendor share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7% (Pacific Plumbing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;50%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active crew size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trim phase coordination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3 2026 forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan early</t>
   </si>
   <si>
     <t xml:space="preserve">JDR Reconciliation</t>
@@ -741,6 +1164,15 @@
   </si>
   <si>
     <t xml:space="preserve">Initial build for #2109 cancelled project. 17-tab JCR schema on revised budget basis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1.1 · enriched</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enriched Job Info tab with 12-section sectioned layout (identity / schedule / contract &amp; financials / scope / project team — 4 sub-sections / AP vendor profile / document meta / data sources / risk flags + actions). Corrected status from 'CANCELLED' (template default) to 'ACTIVE · Roughin phase'. Predictive Signals expanded with active-project signals.</t>
   </si>
 </sst>
 </file>
@@ -755,7 +1187,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
     <numFmt numFmtId="169" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -787,9 +1219,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF70655C"/>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF155724"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -841,14 +1273,61 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF6B6B6B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF2C2B29"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF70655C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -858,28 +1337,86 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2C2B29"/>
-        <bgColor rgb="FF333300"/>
+        <bgColor rgb="FF1F1F1F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8CEC3"/>
-        <bgColor rgb="FFD5DEC5"/>
+        <fgColor rgb="FFECF0F1"/>
+        <bgColor rgb="FFFFF8E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD5DEC5"/>
-        <bgColor rgb="FFE8CEC3"/>
+        <fgColor rgb="FF2C3E50"/>
+        <bgColor rgb="FF2C2B29"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E7"/>
+        <bgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor rgb="FFD1ECF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1ECF1"/>
+        <bgColor rgb="FFD4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFF8E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor rgb="FFD5D8DC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD5D8DC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD5D8DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD5D8DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD5D8DC"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD5D8DC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -923,24 +1460,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -964,12 +1505,72 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -978,6 +1579,10 @@
     </xf>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1012,16 +1617,52 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1050,15 +1691,15 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFB8AE"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF70655C"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFFF3CD"/>
+      <rgbColor rgb="FFD1ECF1"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD5DEC5"/>
+      <rgbColor rgb="FFD5D8DC"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1068,28 +1709,28 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFECF0F1"/>
+      <rgbColor rgb="FFD4EDDA"/>
+      <rgbColor rgb="FFFFF8E7"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFE8CEC3"/>
+      <rgbColor rgb="FFF8D7DA"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF70655C"/>
+      <rgbColor rgb="FF6B6B6B"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF155724"/>
+      <rgbColor rgb="FF1F1F1F"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF2C3E50"/>
       <rgbColor rgb="FF2C2B29"/>
     </indexedColors>
   </colors>
@@ -1276,156 +1917,538 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>3718851</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>2119967.36</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <f aca="false">B5-B6</f>
         <v>1598883.64</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <f aca="false">IFERROR(B7/B5,0)</f>
         <v>0.429940226161253</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>3570012</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>153880.15</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="7" t="n">
         <f aca="false">B11-B12</f>
         <v>3416131.85</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="7" t="n">
         <f aca="false">B5-B11</f>
         <v>148839</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="8" t="n">
         <f aca="false">IFERROR(B11/B5,0)</f>
         <v>0.959977154233929</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="10" t="n">
         <v>-349534.48</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="10" t="n">
         <v>1071980.16</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B21" s="10" t="n">
         <v>1468646.78</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="10" t="n">
         <v>-3077603</v>
       </c>
     </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="12"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="12"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+    </row>
+    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+    </row>
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+    </row>
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="12"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="12"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="12"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="12"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="12"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="12"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="12"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="12"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="12"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="12"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1444,572 +2467,572 @@
   <dimension ref="A1:E33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B4" s="16" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B4" s="33" t="n">
         <v>168</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>11592</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="34" t="n">
         <f aca="false">IFERROR(C4/B4,0)</f>
         <v>69</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="16" t="n">
+      <c r="E4" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B5" s="33" t="n">
         <v>98</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>5831</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="34" t="n">
         <f aca="false">IFERROR(C5/B5,0)</f>
         <v>59.5</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B6" s="16" t="n">
+      <c r="E5" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" s="33" t="n">
         <v>60</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="17" t="n">
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34" t="n">
         <f aca="false">IFERROR(C6/B6,0)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B7" s="16" t="n">
+      <c r="E6" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="33" t="n">
         <v>28.8</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>1553</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="34" t="n">
         <f aca="false">IFERROR(C7/B7,0)</f>
         <v>53.9236111111111</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B8" s="16" t="n">
+      <c r="E7" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B8" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>572</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="34" t="n">
         <f aca="false">IFERROR(C8/B8,0)</f>
         <v>52</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="16" t="n">
+      <c r="E8" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B9" s="33" t="n">
         <v>8.5</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>238</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="34" t="n">
         <f aca="false">IFERROR(C9/B9,0)</f>
         <v>28</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B10" s="16" t="n">
+      <c r="E9" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B10" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>204</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="34" t="n">
         <f aca="false">IFERROR(C10/B10,0)</f>
         <v>68</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="17" t="n">
+      <c r="E10" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="34" t="n">
         <f aca="false">IFERROR(C11/B11,0)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="17" t="n">
+      <c r="E11" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B12" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="34" t="n">
         <f aca="false">IFERROR(C12/B12,0)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="17" t="n">
+      <c r="E12" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B13" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34" t="n">
         <f aca="false">IFERROR(C13/B13,0)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="17" t="n">
+      <c r="E13" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B14" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="34" t="n">
         <f aca="false">IFERROR(C14/B14,0)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="17" t="n">
+      <c r="E14" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B15" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34" t="n">
         <f aca="false">IFERROR(C15/B15,0)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="17" t="n">
+      <c r="E15" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B16" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="34" t="n">
         <f aca="false">IFERROR(C16/B16,0)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="17" t="n">
+      <c r="E16" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="34" t="n">
         <f aca="false">IFERROR(C17/B17,0)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="17" t="n">
+      <c r="E17" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B18" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34" t="n">
         <f aca="false">IFERROR(C18/B18,0)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="17" t="n">
+      <c r="E18" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="34" t="n">
         <f aca="false">IFERROR(C19/B19,0)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="17" t="n">
+      <c r="E19" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="34" t="n">
         <f aca="false">IFERROR(C20/B20,0)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="17" t="n">
+      <c r="E20" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="34" t="n">
         <f aca="false">IFERROR(C21/B21,0)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="17" t="n">
+      <c r="E21" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="34" t="n">
         <f aca="false">IFERROR(C22/B22,0)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="17" t="n">
+      <c r="E22" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="34" t="n">
         <f aca="false">IFERROR(C23/B23,0)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="17" t="n">
+      <c r="E23" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="34" t="n">
         <f aca="false">IFERROR(C24/B24,0)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="17" t="n">
+      <c r="E24" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B25" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="34" t="n">
         <f aca="false">IFERROR(C25/B25,0)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="17" t="n">
+      <c r="E25" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="34" t="n">
         <f aca="false">IFERROR(C26/B26,0)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="17" t="n">
+      <c r="E26" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B27" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="34" t="n">
         <f aca="false">IFERROR(C27/B27,0)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="17" t="n">
+      <c r="E27" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B28" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="34" t="n">
         <f aca="false">IFERROR(C28/B28,0)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="17" t="n">
+      <c r="E28" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B29" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="34" t="n">
         <f aca="false">IFERROR(C29/B29,0)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="17" t="n">
+      <c r="E29" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B30" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="34" t="n">
         <f aca="false">IFERROR(C30/B30,0)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B31" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="17" t="n">
+      <c r="E30" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B31" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="34" t="n">
         <f aca="false">IFERROR(C31/B31,0)</f>
         <v>0</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="17" t="n">
+      <c r="E31" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B32" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="34" t="n">
         <f aca="false">IFERROR(C32/B32,0)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B33" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="17" t="n">
+      <c r="E32" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="34" t="n">
         <f aca="false">IFERROR(C33/B33,0)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>153</v>
+      <c r="E33" s="5" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -2031,102 +3054,102 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="4" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="33" t="n">
         <v>308.8</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>19752</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="28" t="n">
         <f aca="false">IFERROR(C4/SUM(C$4:C$7),0)</f>
         <v>0.818446859263186</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="B5" s="4" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="33" t="n">
         <v>8.5</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>238</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="28" t="n">
         <f aca="false">IFERROR(C5/SUM(C$4:C$7),0)</f>
         <v>0.022528491916247</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6" s="4" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="33" t="n">
         <v>60</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="12" t="n">
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="28" t="n">
         <f aca="false">IFERROR(C6/SUM(C$4:C$7),0)</f>
         <v>0.159024648820567</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="B7" s="4" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="C7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12" t="n">
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28" t="n">
         <f aca="false">IFERROR(C7/SUM(C$4:C$7),0)</f>
         <v>0</v>
       </c>
@@ -2150,52 +3173,52 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B3" s="16" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B3" s="33" t="n">
         <v>377</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" s="18" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B4" s="35" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B5" s="16" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B5" s="33" t="n">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B6" s="19" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B6" s="36" t="n">
         <v>9463.25</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="37" t="n">
         <v>0.959977154233929</v>
       </c>
     </row>
@@ -2218,85 +3241,85 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B4" s="20" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="37" t="n">
         <v>0.429940226161253</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="37" t="n">
         <v>0.34</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="28" t="n">
         <f aca="false">B4-C4</f>
-        <v>0.0899402261612525</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="20" t="n">
+        <v>0.089940226161253</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B5" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="37" t="n">
         <v>0.45</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="28" t="n">
         <f aca="false">B5-C5</f>
         <v>-0.45</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B6" s="20" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" s="37" t="n">
         <v>0.467237248122204</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="37" t="n">
         <v>0.38</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="28" t="n">
         <f aca="false">B6-C6</f>
-        <v>0.0872372481222041</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B7" s="16" t="n">
+        <v>0.087237248122204</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B7" s="33" t="n">
         <v>1.53353658536585</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="33" t="n">
         <v>95</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="38" t="n">
         <f aca="false">B7-C7</f>
         <v>-93.4664634146342</v>
       </c>
@@ -2317,73 +3340,387 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>310</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>312</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>313</v>
+      </c>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>314</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>315</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>318</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>320</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>321</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>322</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="F6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>323</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>324</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>325</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>203</v>
-      </c>
+      <c r="B9" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>328</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="F10" s="12"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>330</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>331</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>333</v>
+      </c>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>334</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>335</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>336</v>
+      </c>
+      <c r="F12" s="12"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>337</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>338</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>339</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="42" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>340</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>328</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>342</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>343</v>
+      </c>
+      <c r="D15" s="42" t="s">
+        <v>344</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2404,91 +3741,91 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B4" s="5" t="n">
+      <c r="B3" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>347</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>2683501.46</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>1738893.19</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="10" t="n">
         <f aca="false">IF(ISNUMBER(B4),B4-C4,"—")</f>
         <v>944608.27</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B5" s="5" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>-3570012</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>3077603</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="10" t="n">
         <f aca="false">IF(ISNUMBER(B5),B5-C5,"—")</f>
         <v>-6647615</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C6" s="5" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" s="6" t="n">
         <v>1071980.16</v>
       </c>
-      <c r="D6" s="9" t="str">
+      <c r="D6" s="10" t="str">
         <f aca="false">IF(ISNUMBER(B6),B6-C6,"—")</f>
         <v>—</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C7" s="5" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C7" s="6" t="n">
         <v>1468646.78</v>
       </c>
-      <c r="D7" s="9" t="str">
+      <c r="D7" s="10" t="str">
         <f aca="false">IF(ISNUMBER(B7),B7-C7,"—")</f>
         <v>—</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C8" s="5" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="C8" s="6" t="n">
         <v>-349534.48</v>
       </c>
-      <c r="D8" s="9" t="str">
+      <c r="D8" s="10" t="str">
         <f aca="false">IF(ISNUMBER(B8),B8-C8,"—")</f>
         <v>—</v>
       </c>
@@ -2512,91 +3849,91 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>354</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="47" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>227</v>
+      <c r="B5" s="47" t="s">
+        <v>356</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="47" t="s">
+        <v>359</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>360</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="47" t="s">
+        <v>307</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>362</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="47" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>364</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="47" t="s">
+        <v>366</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>367</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -2615,39 +3952,50 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>234</v>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>370</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>371</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="48" t="s">
+        <v>376</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>377</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -2666,115 +4014,1027 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="28"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="18"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="22" t="n">
+        <v>246</v>
+      </c>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="15" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+      <c r="B40" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="15" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+      <c r="B46" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B48" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+      <c r="B49" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B53" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" s="25"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
+      <c r="B59" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="C59" s="25"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="25"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B60" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" s="25"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B61" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B63" s="24"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C64" s="25"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="25"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B65" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="25"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B66" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B67" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C67" s="25"/>
+      <c r="D67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="25"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="B69" s="24"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B71" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B72" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="B75" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B76" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
+    </row>
+    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B77" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="C77" s="22"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="22"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B79" s="24"/>
+      <c r="C79" s="24"/>
+      <c r="D79" s="24"/>
+      <c r="E79" s="24"/>
+      <c r="F79" s="24"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B80" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="22"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B81" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="C81" s="22"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="B82" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="22"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="B83" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="22"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="B84" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="C84" s="22"/>
+      <c r="D84" s="22"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B86" s="24"/>
+      <c r="C86" s="24"/>
+      <c r="D86" s="24"/>
+      <c r="E86" s="24"/>
+      <c r="F86" s="24"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B87" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="C87" s="25"/>
+      <c r="D87" s="25"/>
+      <c r="E87" s="25"/>
+      <c r="F87" s="25"/>
+    </row>
+    <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B88" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C88" s="25"/>
+      <c r="D88" s="25"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+    </row>
+    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B89" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C89" s="25"/>
+      <c r="D89" s="25"/>
+      <c r="E89" s="25"/>
+      <c r="F89" s="25"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B90" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="C90" s="25"/>
+      <c r="D90" s="25"/>
+      <c r="E90" s="25"/>
+      <c r="F90" s="25"/>
     </row>
   </sheetData>
+  <mergeCells count="78">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B76:F76"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2793,90 +5053,90 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="5" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>3700937</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>3718851</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="10" t="n">
         <f aca="false">C4-B4</f>
         <v>17914</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="5" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>17914</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="10" t="n">
         <f aca="false">C5-B5</f>
         <v>17914</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="6" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="7" t="n">
         <f aca="false">SUM(B4:B5)</f>
         <v>3700937</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <f aca="false">SUM(C4:C5)</f>
         <v>3736765</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <f aca="false">SUM(D4:D5)</f>
         <v>35828</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>51</v>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2898,36 +5158,36 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>59</v>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2949,33 +5209,33 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>36</v>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2997,571 +5257,571 @@
   <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="5" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="6" t="n">
         <v>18450</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>18450</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>4071</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="10" t="n">
         <f aca="false">D4-E4</f>
         <v>14379</v>
       </c>
-      <c r="G4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="12" t="n">
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="28" t="n">
         <f aca="false">IFERROR(E4/D4,0)</f>
         <v>0.220650406504065</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="5" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>24600</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>24600</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>15235</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <f aca="false">D5-E5</f>
         <v>9365</v>
       </c>
-      <c r="G5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="12" t="n">
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="28" t="n">
         <f aca="false">IFERROR(E5/D5,0)</f>
         <v>0.619308943089431</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="9" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10" t="n">
         <f aca="false">D6-E6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="12" t="n">
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="n">
         <f aca="false">IFERROR(E6/D6,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>14.25</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <f aca="false">D7-E7</f>
         <v>-14.25</v>
       </c>
-      <c r="G7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="12" t="n">
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="n">
         <f aca="false">IFERROR(E7/D7,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>675</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>670</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="10" t="n">
         <f aca="false">D8-E8</f>
         <v>5</v>
       </c>
-      <c r="G8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="12" t="n">
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n">
         <f aca="false">IFERROR(E8/D8,0)</f>
         <v>0.992592592592593</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="5" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" s="6" t="n">
         <v>96801</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>96801</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>55460.25</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <f aca="false">D9-E9</f>
         <v>41340.75</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="12" t="n">
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n">
         <f aca="false">IFERROR(E9/D9,0)</f>
         <v>0.572930548238138</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="5" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" s="6" t="n">
         <v>454876</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="6" t="n">
         <v>454876</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="6" t="n">
         <v>464398.31</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <f aca="false">D10-E10</f>
         <v>-9522.31</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <v>8449.81</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="28" t="n">
         <f aca="false">IFERROR(E10/D10,0)</f>
         <v>1.02093385889781</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="5" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C11" s="6" t="n">
         <v>835857</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>838640</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="6" t="n">
         <v>621810.17</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <f aca="false">D11-E11</f>
         <v>216829.83</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="6" t="n">
         <v>95810.87</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="28" t="n">
         <f aca="false">IFERROR(E11/D11,0)</f>
         <v>0.741450646284461</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="9" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10" t="n">
         <f aca="false">D12-E12</f>
         <v>0</v>
       </c>
-      <c r="G12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12" t="n">
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="28" t="n">
         <f aca="false">IFERROR(E12/D12,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="9" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10" t="n">
         <f aca="false">D13-E13</f>
         <v>0</v>
       </c>
-      <c r="G13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12" t="n">
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="28" t="n">
         <f aca="false">IFERROR(E13/D13,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="5" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="n">
         <v>2568.72</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="10" t="n">
         <f aca="false">D14-E14</f>
         <v>-2568.72</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="6" t="n">
         <v>2517.35</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="H14" s="28" t="n">
         <f aca="false">IFERROR(E14/D14,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="5" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" s="6" t="n">
         <v>26000</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="6" t="n">
         <v>26000</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="6" t="n">
         <v>2409.88</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="10" t="n">
         <f aca="false">D15-E15</f>
         <v>23590.12</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="6" t="n">
         <v>1334.68</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="28" t="n">
         <f aca="false">IFERROR(E15/D15,0)</f>
         <v>0.0926876923076923</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="5" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C16" s="6" t="n">
         <v>5850</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="6" t="n">
         <v>5850</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="6" t="n">
         <v>22320</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="10" t="n">
         <f aca="false">D16-E16</f>
         <v>-16470</v>
       </c>
-      <c r="G16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="12" t="n">
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="28" t="n">
         <f aca="false">IFERROR(E16/D16,0)</f>
         <v>3.81538461538462</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="5" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6" t="n">
         <v>2472.45</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <f aca="false">D17-E17</f>
         <v>-2472.45</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="6" t="n">
         <v>262.14</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="H17" s="28" t="n">
         <f aca="false">IFERROR(E17/D17,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="5" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" s="6" t="n">
         <v>102758</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="6" t="n">
         <v>102758</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="6" t="n">
         <v>39307.9</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="10" t="n">
         <f aca="false">D18-E18</f>
         <v>63450.1</v>
       </c>
-      <c r="G18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="12" t="n">
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="28" t="n">
         <f aca="false">IFERROR(E18/D18,0)</f>
         <v>0.382528854201133</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="5" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C19" s="6" t="n">
         <v>12450</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="6" t="n">
         <v>12450</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="6" t="n">
         <v>5515</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="10" t="n">
         <f aca="false">D19-E19</f>
         <v>6935</v>
       </c>
-      <c r="G19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="12" t="n">
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="28" t="n">
         <f aca="false">IFERROR(E19/D19,0)</f>
         <v>0.442971887550201</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" s="5" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C20" s="6" t="n">
         <v>444827.57</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" s="6" t="n">
         <v>448466.07</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="6" t="n">
         <v>428740.41</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="10" t="n">
         <f aca="false">D20-E20</f>
         <v>19725.66</v>
       </c>
-      <c r="G20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="12" t="n">
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="28" t="n">
         <f aca="false">IFERROR(E20/D20,0)</f>
         <v>0.956015267777114</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C21" s="5" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C21" s="6" t="n">
         <v>89668.8</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="6" t="n">
         <v>90401.29</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="6" t="n">
         <v>73899.85</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="10" t="n">
         <f aca="false">D21-E21</f>
         <v>16501.44</v>
       </c>
-      <c r="G21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="12" t="n">
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="28" t="n">
         <f aca="false">IFERROR(E21/D21,0)</f>
         <v>0.817464551667349</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" s="6" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="C22" s="7" t="n">
         <f aca="false">SUM(C4:C21)</f>
         <v>2112138.37</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="7" t="n">
         <f aca="false">SUM(D4:D21)</f>
         <v>2119967.36</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <f aca="false">SUM(E4:E21)</f>
         <v>1738893.19</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <f aca="false">SUM(F4:F21)</f>
         <v>381074.17</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <f aca="false">SUM(G4:G21)</f>
         <v>108374.85</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H22" s="8" t="n">
         <f aca="false">IFERROR(E22/D22,0)</f>
         <v>0.820245265474276</v>
       </c>
@@ -3585,145 +5845,145 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4" s="4" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>43050</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>19320.25</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="10" t="n">
         <f aca="false">C4-D4</f>
         <v>23729.75</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="28" t="n">
         <f aca="false">IFERROR(D4/C4,0)</f>
         <v>0.448786295005807</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5" s="4" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>1390317</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>1144237.45</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="10" t="n">
         <f aca="false">C5-D5</f>
         <v>246079.55</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="28" t="n">
         <f aca="false">IFERROR(D5/C5,0)</f>
         <v>0.823004717629145</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="4" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>147058</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>72025.23</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <f aca="false">C6-D6</f>
         <v>75032.77</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="28" t="n">
         <f aca="false">IFERROR(D6/C6,0)</f>
         <v>0.489774306736118</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="4" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>538867.36</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>502640.26</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <f aca="false">C7-D7</f>
         <v>36227.1</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="28" t="n">
         <f aca="false">IFERROR(D7/C7,0)</f>
         <v>0.932771767805718</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="B8" s="13" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" s="29" t="n">
         <f aca="false">SUM(B4:B7)</f>
         <v>17</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <f aca="false">SUM(C4:C7)</f>
         <v>2119292.36</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <f aca="false">SUM(D4:D7)</f>
         <v>1738223.19</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <f aca="false">SUM(E4:E7)</f>
         <v>381069.17</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <f aca="false">IFERROR(D8/C8,0)</f>
         <v>0.820190372412799</v>
       </c>
@@ -3747,432 +6007,432 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="5" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>18450</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>4071</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="10" t="n">
         <f aca="false">C5-D5</f>
         <v>14379</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="28" t="n">
         <f aca="false">IFERROR((D5-C5)/C5,0)</f>
         <v>-0.779349593495935</v>
       </c>
-      <c r="G5" s="14" t="str">
+      <c r="G5" s="31" t="str">
         <f aca="false">IF(C5=0,"UNBUDGETED",IF(F5&gt;0.5,"CRITICAL",IF(F5&gt;0.1,"OVER",IF(F5&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="5" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="6" t="n">
         <v>24600</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>15235</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <f aca="false">C6-D6</f>
         <v>9365</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="28" t="n">
         <f aca="false">IFERROR((D6-C6)/C6,0)</f>
         <v>-0.380691056910569</v>
       </c>
-      <c r="G6" s="14" t="str">
+      <c r="G6" s="31" t="str">
         <f aca="false">IF(C6=0,"UNBUDGETED",IF(F6&gt;0.5,"CRITICAL",IF(F6&gt;0.1,"OVER",IF(F6&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>14.25</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <f aca="false">C7-D7</f>
         <v>-14.25</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="28" t="n">
         <f aca="false">IFERROR((D7-C7)/C7,0)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="14" t="str">
+      <c r="G7" s="31" t="str">
         <f aca="false">IF(C7=0,"UNBUDGETED",IF(F7&gt;0.5,"CRITICAL",IF(F7&gt;0.1,"OVER",IF(F7&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="5" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" s="6" t="n">
         <v>675</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>670</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <f aca="false">C8-D8</f>
         <v>5</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="28" t="n">
         <f aca="false">IFERROR((D8-C8)/C8,0)</f>
         <v>-0.00740740740740741</v>
       </c>
-      <c r="G8" s="14" t="str">
+      <c r="G8" s="31" t="str">
         <f aca="false">IF(C8=0,"UNBUDGETED",IF(F8&gt;0.5,"CRITICAL",IF(F8&gt;0.1,"OVER",IF(F8&lt;-0.1,"UNDER","ON"))))</f>
         <v>ON</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="5" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" s="6" t="n">
         <v>96801</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>55460.25</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="10" t="n">
         <f aca="false">C9-D9</f>
         <v>41340.75</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="28" t="n">
         <f aca="false">IFERROR((D9-C9)/C9,0)</f>
         <v>-0.427069451761862</v>
       </c>
-      <c r="G9" s="14" t="str">
+      <c r="G9" s="31" t="str">
         <f aca="false">IF(C9=0,"UNBUDGETED",IF(F9&gt;0.5,"CRITICAL",IF(F9&gt;0.1,"OVER",IF(F9&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="5" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" s="6" t="n">
         <v>454876</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="6" t="n">
         <v>464398.31</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <f aca="false">C10-D10</f>
         <v>-9522.31</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="28" t="n">
         <f aca="false">IFERROR((D10-C10)/C10,0)</f>
         <v>0.0209338588978095</v>
       </c>
-      <c r="G10" s="14" t="str">
+      <c r="G10" s="31" t="str">
         <f aca="false">IF(C10=0,"UNBUDGETED",IF(F10&gt;0.5,"CRITICAL",IF(F10&gt;0.1,"OVER",IF(F10&lt;-0.1,"UNDER","ON"))))</f>
         <v>ON</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="5" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C11" s="6" t="n">
         <v>838640</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>621810.17</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <f aca="false">C11-D11</f>
         <v>216829.83</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="28" t="n">
         <f aca="false">IFERROR((D11-C11)/C11,0)</f>
         <v>-0.258549353715539</v>
       </c>
-      <c r="G11" s="14" t="str">
+      <c r="G11" s="31" t="str">
         <f aca="false">IF(C11=0,"UNBUDGETED",IF(F11&gt;0.5,"CRITICAL",IF(F11&gt;0.1,"OVER",IF(F11&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="5" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
         <v>2568.72</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="10" t="n">
         <f aca="false">C12-D12</f>
         <v>-2568.72</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="28" t="n">
         <f aca="false">IFERROR((D12-C12)/C12,0)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="14" t="str">
+      <c r="G12" s="31" t="str">
         <f aca="false">IF(C12=0,"UNBUDGETED",IF(F12&gt;0.5,"CRITICAL",IF(F12&gt;0.1,"OVER",IF(F12&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C13" s="5" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C13" s="6" t="n">
         <v>26000</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="6" t="n">
         <v>2409.88</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="10" t="n">
         <f aca="false">C13-D13</f>
         <v>23590.12</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="28" t="n">
         <f aca="false">IFERROR((D13-C13)/C13,0)</f>
         <v>-0.907312307692308</v>
       </c>
-      <c r="G13" s="14" t="str">
+      <c r="G13" s="31" t="str">
         <f aca="false">IF(C13=0,"UNBUDGETED",IF(F13&gt;0.5,"CRITICAL",IF(F13&gt;0.1,"OVER",IF(F13&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="5" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C14" s="6" t="n">
         <v>5850</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="6" t="n">
         <v>22320</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="10" t="n">
         <f aca="false">C14-D14</f>
         <v>-16470</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" s="28" t="n">
         <f aca="false">IFERROR((D14-C14)/C14,0)</f>
         <v>2.81538461538462</v>
       </c>
-      <c r="G14" s="14" t="str">
+      <c r="G14" s="31" t="str">
         <f aca="false">IF(C14=0,"UNBUDGETED",IF(F14&gt;0.5,"CRITICAL",IF(F14&gt;0.1,"OVER",IF(F14&lt;-0.1,"UNDER","ON"))))</f>
         <v>CRITICAL</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="5" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="6" t="n">
         <v>2472.45</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="10" t="n">
         <f aca="false">C15-D15</f>
         <v>-2472.45</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="28" t="n">
         <f aca="false">IFERROR((D15-C15)/C15,0)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="14" t="str">
+      <c r="G15" s="31" t="str">
         <f aca="false">IF(C15=0,"UNBUDGETED",IF(F15&gt;0.5,"CRITICAL",IF(F15&gt;0.1,"OVER",IF(F15&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="5" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C16" s="6" t="n">
         <v>102758</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="6" t="n">
         <v>39307.9</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="10" t="n">
         <f aca="false">C16-D16</f>
         <v>63450.1</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="28" t="n">
         <f aca="false">IFERROR((D16-C16)/C16,0)</f>
         <v>-0.617471145798867</v>
       </c>
-      <c r="G16" s="14" t="str">
+      <c r="G16" s="31" t="str">
         <f aca="false">IF(C16=0,"UNBUDGETED",IF(F16&gt;0.5,"CRITICAL",IF(F16&gt;0.1,"OVER",IF(F16&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="5" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C17" s="6" t="n">
         <v>12450</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="6" t="n">
         <v>5515</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="10" t="n">
         <f aca="false">C17-D17</f>
         <v>6935</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="28" t="n">
         <f aca="false">IFERROR((D17-C17)/C17,0)</f>
         <v>-0.557028112449799</v>
       </c>
-      <c r="G17" s="14" t="str">
+      <c r="G17" s="31" t="str">
         <f aca="false">IF(C17=0,"UNBUDGETED",IF(F17&gt;0.5,"CRITICAL",IF(F17&gt;0.1,"OVER",IF(F17&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" s="5" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C18" s="6" t="n">
         <v>448466.07</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="6" t="n">
         <v>428740.41</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="10" t="n">
         <f aca="false">C18-D18</f>
         <v>19725.66</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="28" t="n">
         <f aca="false">IFERROR((D18-C18)/C18,0)</f>
         <v>-0.043984732222886</v>
       </c>
-      <c r="G18" s="14" t="str">
+      <c r="G18" s="31" t="str">
         <f aca="false">IF(C18=0,"UNBUDGETED",IF(F18&gt;0.5,"CRITICAL",IF(F18&gt;0.1,"OVER",IF(F18&lt;-0.1,"UNDER","ON"))))</f>
         <v>ON</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="5" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C19" s="6" t="n">
         <v>90401.29</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="6" t="n">
         <v>73899.85</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="10" t="n">
         <f aca="false">C19-D19</f>
         <v>16501.44</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="28" t="n">
         <f aca="false">IFERROR((D19-C19)/C19,0)</f>
         <v>-0.182535448332651</v>
       </c>
-      <c r="G19" s="14" t="str">
+      <c r="G19" s="31" t="str">
         <f aca="false">IF(C19=0,"UNBUDGETED",IF(F19&gt;0.5,"CRITICAL",IF(F19&gt;0.1,"OVER",IF(F19&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
@@ -4196,235 +6456,235 @@
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" s="5" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>500869.06</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="28" t="n">
         <f aca="false">IFERROR(B4/SUM(B$4:B$16),0)</f>
         <v>0.467237248122204</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B5" s="5" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>305149.79</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="28" t="n">
         <f aca="false">IFERROR(B5/SUM(B$4:B$16),0)</f>
         <v>0.284659923183653</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="5" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>103987.31</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="28" t="n">
         <f aca="false">IFERROR(B6/SUM(B$4:B$16),0)</f>
-        <v>0.0970048830008198</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B7" s="5" t="n">
+        <v>0.0970048830008197</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>76546</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="28" t="n">
         <f aca="false">IFERROR(B7/SUM(B$4:B$16),0)</f>
         <v>0.071406172293338</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" s="5" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>52035.97</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="28" t="n">
         <f aca="false">IFERROR(B8/SUM(B$4:B$16),0)</f>
         <v>0.0485419151787287</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B9" s="5" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>22320</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="28" t="n">
         <f aca="false">IFERROR(B9/SUM(B$4:B$16),0)</f>
         <v>0.0208212808714669</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B10" s="5" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>2472.45</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="28" t="n">
         <f aca="false">IFERROR(B10/SUM(B$4:B$16),0)</f>
         <v>0.00230643261158863</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B11" s="5" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" s="6" t="n">
         <v>2408</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="28" t="n">
         <f aca="false">IFERROR(B11/SUM(B$4:B$16),0)</f>
         <v>0.00224631023021919</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B12" s="5" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B12" s="6" t="n">
         <v>1983.84</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="28" t="n">
         <f aca="false">IFERROR(B12/SUM(B$4:B$16),0)</f>
         <v>0.00185063126541446</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B13" s="5" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B13" s="6" t="n">
         <v>1865.27</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="28" t="n">
         <f aca="false">IFERROR(B13/SUM(B$4:B$16),0)</f>
         <v>0.00174002287505023</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B14" s="5" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B14" s="6" t="n">
         <v>1602.9</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="28" t="n">
         <f aca="false">IFERROR(B14/SUM(B$4:B$16),0)</f>
         <v>0.00149527021097107</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15" s="5" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B15" s="6" t="n">
         <v>544.61</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="28" t="n">
         <f aca="false">IFERROR(B15/SUM(B$4:B$16),0)</f>
         <v>0.000508041118969963</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B16" s="5" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B16" s="6" t="n">
         <v>194.96</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="28" t="n">
         <f aca="false">IFERROR(B16/SUM(B$4:B$16),0)</f>
         <v>0.000181869037576218</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="B17" s="6" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="B17" s="7" t="n">
         <f aca="false">SUM(B4:B16)</f>
         <v>1071980.16</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="32" t="n">
         <f aca="false">SUM(C4:C16)</f>
         <v>436</v>
       </c>

--- a/owp/owp-2109-live/cortex output files/OWP_2109_JCR_Cortex_v2.xlsx
+++ b/owp/owp-2109-live/cortex output files/OWP_2109_JCR_Cortex_v2.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="386">
   <si>
     <t xml:space="preserve">OWP #2109 · Marysville Ph2</t>
   </si>
@@ -320,10 +320,25 @@
     <t xml:space="preserve">Plumbing Units</t>
   </si>
   <si>
+    <t xml:space="preserve">246  ⚠ UNVERIFIED ESTIMATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Units provenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠ UNVERIFIED ESTIMATE — set by prior session in parse_2109.py PROJECT_META. JDR has no unit count. No GDrive folder mounted. Must be confirmed against drawing P001 or OWP bid sheet once available. (Phase 1 = #2097 Intracorp Marysville — Job Book folder exists but is empty.)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total Fixtures</t>
   </si>
   <si>
-    <t xml:space="preserve">TBD (fixture schedule not yet finalized in this dataset)</t>
+    <t xml:space="preserve">UNKNOWN  ⚠ no fixture schedule available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixtures provenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNKNOWN — no fixture schedule available. 30 workers + 377 hrs logged YTD, $3.57M billed → this is an active project, fixture data should exist in Sage purchase orders + GDrive submittals.</t>
   </si>
   <si>
     <t xml:space="preserve">Floors</t>
@@ -1173,6 +1188,12 @@
   </si>
   <si>
     <t xml:space="preserve">Enriched Job Info tab with 12-section sectioned layout (identity / schedule / contract &amp; financials / scope / project team — 4 sub-sections / AP vendor profile / document meta / data sources / risk flags + actions). Corrected status from 'CANCELLED' (template default) to 'ACTIVE · Roughin phase'. Predictive Signals expanded with active-project signals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1.2 · units audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audited unit/fixture counts. Units 246 flagged as UNVERIFIED ESTIMATE (no source-doc verification possible — JDR has no unit count, no GDrive folder mounted). Fixtures marked UNKNOWN.</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1208,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
     <numFmt numFmtId="169" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1319,6 +1340,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF9A4F02"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF70655C"/>
@@ -1360,6 +1389,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFF8E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD4EDDA"/>
         <bgColor rgb="FFD1ECF1"/>
       </patternFill>
@@ -1372,18 +1407,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-        <bgColor rgb="FFFFF8E7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF8D7DA"/>
         <bgColor rgb="FFD5D8DC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1410,6 +1439,17 @@
       <left style="thin">
         <color rgb="FFD5D8DC"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD5D8DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
       <right/>
       <top style="thin">
         <color rgb="FFD5D8DC"/>
@@ -1460,7 +1500,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1505,23 +1545,19 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1533,11 +1569,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1553,11 +1585,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1565,12 +1613,12 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1581,7 +1629,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1617,6 +1665,10 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1629,23 +1681,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1653,16 +1701,20 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1728,7 +1780,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF155724"/>
       <rgbColor rgb="FF1F1F1F"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF9A4F02"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2C3E50"/>
       <rgbColor rgb="FF2C2B29"/>
@@ -2066,7 +2118,7 @@
         <v>-3077603</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
         <v>20</v>
       </c>
@@ -2076,373 +2128,260 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="11"/>
-      <c r="H40" s="12"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="s">
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="12"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="14" t="s">
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="15" t="s">
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-    </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="15" t="s">
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-    </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="15" t="s">
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="15" t="s">
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="15" t="s">
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-    </row>
-    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15" t="s">
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="15" t="s">
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-    </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="15" t="s">
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-    </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15" t="s">
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="15" t="s">
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="15" t="s">
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="15" t="s">
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="15" t="s">
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="B56" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="15" t="s">
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="15" t="s">
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="12"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="12"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="12"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="12"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="12"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="12"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="12"/>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="12"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2475,564 +2414,564 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>258</v>
+      <c r="A3" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B4" s="33" t="n">
+        <v>264</v>
+      </c>
+      <c r="B4" s="35" t="n">
         <v>168</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11592</v>
       </c>
-      <c r="D4" s="34" t="n">
+      <c r="D4" s="36" t="n">
         <f aca="false">IFERROR(C4/B4,0)</f>
         <v>69</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B5" s="33" t="n">
+        <v>266</v>
+      </c>
+      <c r="B5" s="35" t="n">
         <v>98</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>5831</v>
       </c>
-      <c r="D5" s="34" t="n">
+      <c r="D5" s="36" t="n">
         <f aca="false">IFERROR(C5/B5,0)</f>
         <v>59.5</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B6" s="33" t="n">
+        <v>267</v>
+      </c>
+      <c r="B6" s="35" t="n">
         <v>60</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="36" t="n">
         <f aca="false">IFERROR(C6/B6,0)</f>
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B7" s="33" t="n">
+        <v>269</v>
+      </c>
+      <c r="B7" s="35" t="n">
         <v>28.8</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1553</v>
       </c>
-      <c r="D7" s="34" t="n">
+      <c r="D7" s="36" t="n">
         <f aca="false">IFERROR(C7/B7,0)</f>
         <v>53.9236111111111</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B8" s="33" t="n">
+        <v>270</v>
+      </c>
+      <c r="B8" s="35" t="n">
         <v>11</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>572</v>
       </c>
-      <c r="D8" s="34" t="n">
+      <c r="D8" s="36" t="n">
         <f aca="false">IFERROR(C8/B8,0)</f>
         <v>52</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B9" s="33" t="n">
+        <v>271</v>
+      </c>
+      <c r="B9" s="35" t="n">
         <v>8.5</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>238</v>
       </c>
-      <c r="D9" s="34" t="n">
+      <c r="D9" s="36" t="n">
         <f aca="false">IFERROR(C9/B9,0)</f>
         <v>28</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="B10" s="33" t="n">
+        <v>273</v>
+      </c>
+      <c r="B10" s="35" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>204</v>
       </c>
-      <c r="D10" s="34" t="n">
+      <c r="D10" s="36" t="n">
         <f aca="false">IFERROR(C10/B10,0)</f>
         <v>68</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="B11" s="33" t="n">
+        <v>274</v>
+      </c>
+      <c r="B11" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="34" t="n">
+      <c r="D11" s="36" t="n">
         <f aca="false">IFERROR(C11/B11,0)</f>
         <v>0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B12" s="33" t="n">
+        <v>276</v>
+      </c>
+      <c r="B12" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D12" s="36" t="n">
         <f aca="false">IFERROR(C12/B12,0)</f>
         <v>0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="B13" s="33" t="n">
+        <v>277</v>
+      </c>
+      <c r="B13" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="34" t="n">
+      <c r="D13" s="36" t="n">
         <f aca="false">IFERROR(C13/B13,0)</f>
         <v>0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="B14" s="33" t="n">
+        <v>278</v>
+      </c>
+      <c r="B14" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="34" t="n">
+      <c r="D14" s="36" t="n">
         <f aca="false">IFERROR(C14/B14,0)</f>
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="B15" s="33" t="n">
+        <v>279</v>
+      </c>
+      <c r="B15" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="34" t="n">
+      <c r="D15" s="36" t="n">
         <f aca="false">IFERROR(C15/B15,0)</f>
         <v>0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="36" t="n">
+        <f aca="false">IFERROR(C16/B16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>275</v>
-      </c>
-      <c r="B16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="34" t="n">
-        <f aca="false">IFERROR(C16/B16,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="B17" s="33" t="n">
+        <v>281</v>
+      </c>
+      <c r="B17" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="34" t="n">
+      <c r="D17" s="36" t="n">
         <f aca="false">IFERROR(C17/B17,0)</f>
         <v>0</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="B18" s="33" t="n">
+        <v>282</v>
+      </c>
+      <c r="B18" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="34" t="n">
+      <c r="D18" s="36" t="n">
         <f aca="false">IFERROR(C18/B18,0)</f>
         <v>0</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B19" s="33" t="n">
+        <v>283</v>
+      </c>
+      <c r="B19" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="34" t="n">
+      <c r="D19" s="36" t="n">
         <f aca="false">IFERROR(C19/B19,0)</f>
         <v>0</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="B20" s="33" t="n">
+        <v>284</v>
+      </c>
+      <c r="B20" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="34" t="n">
+      <c r="D20" s="36" t="n">
         <f aca="false">IFERROR(C20/B20,0)</f>
         <v>0</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="B21" s="33" t="n">
+        <v>285</v>
+      </c>
+      <c r="B21" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="34" t="n">
+      <c r="D21" s="36" t="n">
         <f aca="false">IFERROR(C21/B21,0)</f>
         <v>0</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="B22" s="33" t="n">
+        <v>286</v>
+      </c>
+      <c r="B22" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="34" t="n">
+      <c r="D22" s="36" t="n">
         <f aca="false">IFERROR(C22/B22,0)</f>
         <v>0</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="B23" s="33" t="n">
+        <v>287</v>
+      </c>
+      <c r="B23" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="34" t="n">
+      <c r="D23" s="36" t="n">
         <f aca="false">IFERROR(C23/B23,0)</f>
         <v>0</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="B24" s="33" t="n">
+        <v>288</v>
+      </c>
+      <c r="B24" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="34" t="n">
+      <c r="D24" s="36" t="n">
         <f aca="false">IFERROR(C24/B24,0)</f>
         <v>0</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="B25" s="33" t="n">
+        <v>289</v>
+      </c>
+      <c r="B25" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="34" t="n">
+      <c r="D25" s="36" t="n">
         <f aca="false">IFERROR(C25/B25,0)</f>
         <v>0</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="B26" s="33" t="n">
+        <v>290</v>
+      </c>
+      <c r="B26" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="34" t="n">
+      <c r="D26" s="36" t="n">
         <f aca="false">IFERROR(C26/B26,0)</f>
         <v>0</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="B27" s="33" t="n">
+        <v>291</v>
+      </c>
+      <c r="B27" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="34" t="n">
+      <c r="D27" s="36" t="n">
         <f aca="false">IFERROR(C27/B27,0)</f>
         <v>0</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B28" s="33" t="n">
+        <v>292</v>
+      </c>
+      <c r="B28" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="34" t="n">
+      <c r="D28" s="36" t="n">
         <f aca="false">IFERROR(C28/B28,0)</f>
         <v>0</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="B29" s="33" t="n">
+        <v>293</v>
+      </c>
+      <c r="B29" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="34" t="n">
+      <c r="D29" s="36" t="n">
         <f aca="false">IFERROR(C29/B29,0)</f>
         <v>0</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="B30" s="33" t="n">
+        <v>294</v>
+      </c>
+      <c r="B30" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="34" t="n">
+      <c r="D30" s="36" t="n">
         <f aca="false">IFERROR(C30/B30,0)</f>
         <v>0</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="B31" s="33" t="n">
+        <v>295</v>
+      </c>
+      <c r="B31" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="34" t="n">
+      <c r="D31" s="36" t="n">
         <f aca="false">IFERROR(C31/B31,0)</f>
         <v>0</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="B32" s="33" t="n">
+        <v>296</v>
+      </c>
+      <c r="B32" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="34" t="n">
+      <c r="D32" s="36" t="n">
         <f aca="false">IFERROR(C32/B32,0)</f>
         <v>0</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="B33" s="33" t="n">
+        <v>297</v>
+      </c>
+      <c r="B33" s="35" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="34" t="n">
+      <c r="D33" s="36" t="n">
         <f aca="false">IFERROR(C33/B33,0)</f>
         <v>0</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -3062,94 +3001,94 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>295</v>
+      <c r="A3" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="27" t="s">
-        <v>260</v>
+      <c r="A4" s="17" t="s">
+        <v>265</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="33" t="n">
+      <c r="C4" s="35" t="n">
         <v>308.8</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>19752</v>
       </c>
-      <c r="E4" s="28" t="n">
+      <c r="E4" s="30" t="n">
         <f aca="false">IFERROR(C4/SUM(C$4:C$7),0)</f>
         <v>0.818446859263186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
-        <v>267</v>
+      <c r="A5" s="17" t="s">
+        <v>272</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="35" t="n">
         <v>8.5</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>238</v>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E5" s="30" t="n">
         <f aca="false">IFERROR(C5/SUM(C$4:C$7),0)</f>
         <v>0.022528491916247</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="s">
-        <v>263</v>
+      <c r="A6" s="17" t="s">
+        <v>268</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="35" t="n">
         <v>60</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="30" t="n">
         <f aca="false">IFERROR(C6/SUM(C$4:C$7),0)</f>
         <v>0.159024648820567</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="s">
-        <v>270</v>
+      <c r="A7" s="17" t="s">
+        <v>275</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="30" t="n">
         <f aca="false">IFERROR(C7/SUM(C$4:C$7),0)</f>
         <v>0</v>
       </c>
@@ -3179,38 +3118,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="B3" s="33" t="n">
+        <v>302</v>
+      </c>
+      <c r="B3" s="35" t="n">
         <v>377</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="B4" s="35" t="n">
+        <v>303</v>
+      </c>
+      <c r="B4" s="37" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="B5" s="33" t="n">
+        <v>304</v>
+      </c>
+      <c r="B5" s="35" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="B6" s="36" t="n">
+        <v>305</v>
+      </c>
+      <c r="B6" s="38" t="n">
         <v>9463.25</v>
       </c>
     </row>
@@ -3218,7 +3157,7 @@
       <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="39" t="n">
         <v>0.959977154233929</v>
       </c>
     </row>
@@ -3247,79 +3186,79 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>162</v>
+      <c r="A3" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>308</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B4" s="37" t="n">
+        <v>310</v>
+      </c>
+      <c r="B4" s="39" t="n">
         <v>0.429940226161253</v>
       </c>
-      <c r="C4" s="37" t="n">
+      <c r="C4" s="39" t="n">
         <v>0.34</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="30" t="n">
         <f aca="false">B4-C4</f>
         <v>0.089940226161253</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B5" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="37" t="n">
+        <v>311</v>
+      </c>
+      <c r="B5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="39" t="n">
         <v>0.45</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="30" t="n">
         <f aca="false">B5-C5</f>
         <v>-0.45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="B6" s="37" t="n">
+        <v>312</v>
+      </c>
+      <c r="B6" s="39" t="n">
         <v>0.467237248122204</v>
       </c>
-      <c r="C6" s="37" t="n">
+      <c r="C6" s="39" t="n">
         <v>0.38</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="30" t="n">
         <f aca="false">B6-C6</f>
         <v>0.087237248122204</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="B7" s="33" t="n">
+        <v>313</v>
+      </c>
+      <c r="B7" s="35" t="n">
         <v>1.53353658536585</v>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="35" t="n">
         <v>95</v>
       </c>
-      <c r="D7" s="38" t="n">
+      <c r="D7" s="40" t="n">
         <f aca="false">B7-C7</f>
         <v>-93.4664634146342</v>
       </c>
@@ -3346,381 +3285,297 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
-        <v>309</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
+      <c r="A1" s="41" t="s">
+        <v>314</v>
+      </c>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="39" t="s">
-        <v>178</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>310</v>
-      </c>
-      <c r="C3" s="39" t="s">
-        <v>311</v>
-      </c>
-      <c r="D3" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="E3" s="39" t="s">
-        <v>313</v>
-      </c>
-      <c r="F3" s="12"/>
+      <c r="A3" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>315</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>317</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>318</v>
+      </c>
+      <c r="F3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="40" t="n">
+      <c r="A4" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="41" t="s">
-        <v>314</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>315</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>317</v>
-      </c>
-      <c r="F4" s="12"/>
+      <c r="B4" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>320</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>321</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>322</v>
+      </c>
+      <c r="F4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="40" t="n">
+      <c r="A5" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="41" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>319</v>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>320</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>317</v>
-      </c>
-      <c r="F5" s="12"/>
+      <c r="B5" s="44" t="s">
+        <v>323</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>324</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>325</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>322</v>
+      </c>
+      <c r="F5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="40" t="n">
+      <c r="A6" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="41" t="s">
-        <v>321</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>319</v>
-      </c>
-      <c r="D6" s="42" t="s">
+      <c r="B6" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>324</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>327</v>
+      </c>
+      <c r="E6" s="45" t="s">
         <v>322</v>
       </c>
-      <c r="E6" s="43" t="s">
-        <v>317</v>
-      </c>
-      <c r="F6" s="12"/>
+      <c r="F6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="40" t="n">
+      <c r="A7" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="42" t="s">
-        <v>323</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>317</v>
-      </c>
-      <c r="F7" s="12"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="n">
+      <c r="D7" s="43" t="s">
+        <v>328</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>322</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="42" t="s">
-        <v>324</v>
-      </c>
-      <c r="D8" s="42" t="s">
-        <v>325</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>317</v>
-      </c>
-      <c r="F8" s="12"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42" t="n">
+      <c r="C8" s="43" t="s">
+        <v>329</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>330</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>322</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="C9" s="42" t="s">
+      <c r="B9" s="43" t="s">
+        <v>331</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="42" t="s">
-        <v>327</v>
-      </c>
-      <c r="E9" s="43" t="s">
-        <v>317</v>
-      </c>
-      <c r="F9" s="12"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="n">
+      <c r="D9" s="43" t="s">
+        <v>332</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>322</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="43" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="42" t="s">
-        <v>328</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>329</v>
-      </c>
-      <c r="F10" s="12"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42" t="n">
+      <c r="D10" s="43" t="s">
+        <v>333</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="43" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="42" t="s">
-        <v>330</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>331</v>
-      </c>
-      <c r="D11" s="42" t="s">
-        <v>332</v>
-      </c>
-      <c r="E11" s="45" t="s">
+      <c r="B11" s="43" t="s">
+        <v>335</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>337</v>
+      </c>
+      <c r="E11" s="47" t="s">
+        <v>338</v>
+      </c>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>339</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>340</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>341</v>
+      </c>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>342</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>343</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>344</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>345</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="D14" s="43" t="s">
         <v>333</v>
       </c>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="C12" s="42" t="s">
+      <c r="E14" s="46" t="s">
         <v>334</v>
       </c>
-      <c r="D12" s="42" t="s">
-        <v>335</v>
-      </c>
-      <c r="E12" s="46" t="s">
-        <v>336</v>
-      </c>
-      <c r="F12" s="12"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="42" t="s">
-        <v>337</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>338</v>
-      </c>
-      <c r="D13" s="42" t="s">
-        <v>339</v>
-      </c>
-      <c r="E13" s="44" t="s">
-        <v>329</v>
-      </c>
-      <c r="F13" s="12"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="42" t="s">
-        <v>340</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>341</v>
-      </c>
-      <c r="D14" s="42" t="s">
-        <v>328</v>
-      </c>
-      <c r="E14" s="44" t="s">
-        <v>329</v>
-      </c>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="42" t="n">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="43" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="42" t="s">
-        <v>342</v>
-      </c>
-      <c r="C15" s="42" t="s">
-        <v>343</v>
-      </c>
-      <c r="D15" s="42" t="s">
-        <v>344</v>
-      </c>
-      <c r="E15" s="44" t="s">
-        <v>329</v>
-      </c>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
+      <c r="B15" s="43" t="s">
+        <v>347</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>348</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>349</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F30" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3747,26 +3602,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>347</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>162</v>
+      <c r="B3" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>2683501.46</v>
@@ -3781,7 +3636,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>-3570012</v>
@@ -3796,7 +3651,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>1071980.16</v>
@@ -3808,7 +3663,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1468646.78</v>
@@ -3820,7 +3675,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>-349534.48</v>
@@ -3856,84 +3711,84 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>354</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>355</v>
+      <c r="A3" s="29" t="s">
+        <v>307</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="47" t="s">
-        <v>305</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>356</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>357</v>
+      <c r="A4" s="49" t="s">
+        <v>310</v>
+      </c>
+      <c r="B4" s="49" t="s">
+        <v>361</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="47" t="s">
-        <v>356</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>358</v>
+      <c r="B5" s="49" t="s">
+        <v>361</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="47" t="s">
-        <v>359</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>360</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>361</v>
+      <c r="A6" s="49" t="s">
+        <v>364</v>
+      </c>
+      <c r="B6" s="49" t="s">
+        <v>365</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="47" t="s">
-        <v>307</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>362</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>363</v>
+      <c r="A7" s="49" t="s">
+        <v>312</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>367</v>
+      </c>
+      <c r="C7" s="49" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="47" t="s">
-        <v>308</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>364</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>365</v>
+      <c r="A8" s="49" t="s">
+        <v>313</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>369</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="47" t="s">
-        <v>366</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>367</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>368</v>
+      <c r="A9" s="49" t="s">
+        <v>371</v>
+      </c>
+      <c r="B9" s="49" t="s">
+        <v>372</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3952,7 +3807,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -3962,40 +3817,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>370</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>372</v>
+      <c r="A3" s="29" t="s">
+        <v>375</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>376</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="48" t="s">
-        <v>376</v>
-      </c>
-      <c r="B5" s="49" t="s">
-        <v>377</v>
-      </c>
-      <c r="C5" s="50" t="s">
-        <v>378</v>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="50" t="s">
+        <v>381</v>
+      </c>
+      <c r="B5" s="51" t="s">
+        <v>382</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="53" t="s">
+        <v>381</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>384</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -4014,945 +3880,1010 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24" t="s">
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24" t="s">
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23" t="s">
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="22" t="n">
-        <v>246</v>
-      </c>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23" t="s">
+      <c r="B34" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+    </row>
+    <row r="35" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
+      <c r="B35" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="B36" s="22" t="s">
+      <c r="A36" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+    </row>
+    <row r="37" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="B37" s="22" t="s">
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B42" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B41" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="B42" s="25" t="s">
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B43" s="25" t="s">
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B45" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="15" t="s">
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B48" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="B47" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="C47" s="25"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="B48" s="25" t="s">
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C48" s="25"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15" t="s">
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B51" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="25"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="15" t="s">
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="C50" s="25"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="B52" s="24"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
+      <c r="B52" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C53" s="25"/>
-      <c r="D53" s="25"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B54" s="25" t="s">
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="C54" s="25"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="24"/>
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B57" s="25" t="s">
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B59" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B58" s="25" t="s">
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C58" s="25"/>
-      <c r="D58" s="25"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="25"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="15" t="s">
+      <c r="C60" s="27"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B59" s="25" t="s">
+      <c r="B61" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C59" s="25"/>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B60" s="25" t="s">
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B62" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C60" s="25"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B61" s="25" t="s">
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="B63" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C61" s="25"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="B63" s="24"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
+      <c r="C63" s="28"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="B64" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="B65" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="C65" s="25"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25"/>
+      <c r="A65" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B65" s="24"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B66" s="25" t="s">
+      <c r="A66" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
+      <c r="B66" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C66" s="27"/>
+      <c r="D66" s="27"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="27"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="B67" s="25" t="s">
+      <c r="A67" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C67" s="25"/>
-      <c r="D67" s="25"/>
-      <c r="E67" s="25"/>
-      <c r="F67" s="25"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="24" t="s">
+      <c r="B67" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="B69" s="24"/>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
+      <c r="C67" s="27"/>
+      <c r="D67" s="27"/>
+      <c r="E67" s="27"/>
+      <c r="F67" s="27"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C68" s="24"/>
+      <c r="D68" s="24"/>
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B69" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="28"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="B70" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="B71" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
+      <c r="A71" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B71" s="24"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="24"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="24"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="B72" s="22" t="s">
+      <c r="A72" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="C72" s="22"/>
-      <c r="D72" s="22"/>
-      <c r="E72" s="22"/>
-      <c r="F72" s="22"/>
+      <c r="B72" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C72" s="20"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="B73" s="22" t="s">
+      <c r="A73" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" s="20"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C74" s="20"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B75" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C73" s="22"/>
-      <c r="D73" s="22"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="B74" s="22" t="s">
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B76" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22"/>
-      <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="B75" s="22" t="s">
+      <c r="C76" s="20"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+    </row>
+    <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B77" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C75" s="22"/>
-      <c r="D75" s="22"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="B76" s="22" t="s">
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B78" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C76" s="22"/>
-      <c r="D76" s="22"/>
-      <c r="E76" s="22"/>
-      <c r="F76" s="22"/>
-    </row>
-    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="B77" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="C77" s="22"/>
-      <c r="D77" s="22"/>
-      <c r="E77" s="22"/>
-      <c r="F77" s="22"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="B79" s="24"/>
-      <c r="C79" s="24"/>
-      <c r="D79" s="24"/>
-      <c r="E79" s="24"/>
-      <c r="F79" s="24"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B79" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C79" s="25"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="25"/>
+      <c r="F79" s="25"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="B80" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="C80" s="22"/>
-      <c r="D80" s="22"/>
-      <c r="E80" s="22"/>
-      <c r="F80" s="22"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="B81" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="C81" s="22"/>
-      <c r="D81" s="22"/>
-      <c r="E81" s="22"/>
-      <c r="F81" s="22"/>
+      <c r="A81" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B81" s="24"/>
+      <c r="C81" s="24"/>
+      <c r="D81" s="24"/>
+      <c r="E81" s="24"/>
+      <c r="F81" s="24"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="B82" s="22" t="s">
+      <c r="A82" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="C82" s="22"/>
-      <c r="D82" s="22"/>
-      <c r="E82" s="22"/>
-      <c r="F82" s="22"/>
+      <c r="B82" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C82" s="20"/>
+      <c r="D82" s="20"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="20"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="B83" s="22" t="s">
+      <c r="A83" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="C83" s="22"/>
-      <c r="D83" s="22"/>
-      <c r="E83" s="22"/>
-      <c r="F83" s="22"/>
+      <c r="B83" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="C83" s="20"/>
+      <c r="D83" s="20"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="20"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="B84" s="22" t="s">
+      <c r="A84" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C84" s="22"/>
-      <c r="D84" s="22"/>
-      <c r="E84" s="22"/>
-      <c r="F84" s="22"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="24" t="s">
+      <c r="B84" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B86" s="24"/>
-      <c r="C86" s="24"/>
-      <c r="D86" s="24"/>
-      <c r="E86" s="24"/>
-      <c r="F86" s="24"/>
+      <c r="C84" s="20"/>
+      <c r="D84" s="20"/>
+      <c r="E84" s="20"/>
+      <c r="F84" s="20"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B85" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="C85" s="24"/>
+      <c r="D85" s="24"/>
+      <c r="E85" s="24"/>
+      <c r="F85" s="24"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="B86" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C86" s="25"/>
+      <c r="D86" s="25"/>
+      <c r="E86" s="25"/>
+      <c r="F86" s="25"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="B87" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="C87" s="25"/>
-      <c r="D87" s="25"/>
-      <c r="E87" s="25"/>
-      <c r="F87" s="25"/>
-    </row>
-    <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="B88" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="C88" s="25"/>
-      <c r="D88" s="25"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-    </row>
-    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="15" t="s">
+      <c r="B87" s="26"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="26"/>
+      <c r="E87" s="26"/>
+      <c r="F87" s="26"/>
+    </row>
+    <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="B89" s="25" t="s">
+      <c r="B88" s="24"/>
+      <c r="C88" s="24"/>
+      <c r="D88" s="24"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+    </row>
+    <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="C89" s="25"/>
-      <c r="D89" s="25"/>
-      <c r="E89" s="25"/>
-      <c r="F89" s="25"/>
+      <c r="B89" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C89" s="27"/>
+      <c r="D89" s="27"/>
+      <c r="E89" s="27"/>
+      <c r="F89" s="27"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="B90" s="25" t="s">
+      <c r="A90" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="C90" s="25"/>
-      <c r="D90" s="25"/>
-      <c r="E90" s="25"/>
-      <c r="F90" s="25"/>
+      <c r="B90" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C90" s="27"/>
+      <c r="D90" s="27"/>
+      <c r="E90" s="27"/>
+      <c r="F90" s="27"/>
+    </row>
+    <row r="91" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="B91" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C91" s="24"/>
+      <c r="D91" s="24"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="24"/>
+    </row>
+    <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B92" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="C92" s="24"/>
+      <c r="D92" s="24"/>
+      <c r="E92" s="24"/>
+      <c r="F92" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="78">
@@ -5059,26 +4990,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>162</v>
+      <c r="A3" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>3700937</v>
@@ -5093,7 +5024,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>0</v>
@@ -5107,8 +5038,8 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="s">
-        <v>165</v>
+      <c r="A6" s="17" t="s">
+        <v>170</v>
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">SUM(B4:B5)</f>
@@ -5125,18 +5056,18 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>169</v>
+      <c r="A10" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -5164,30 +5095,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E3" s="26" t="s">
+      <c r="A3" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="E3" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>176</v>
+      <c r="F3" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -5218,23 +5149,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="E3" s="26" t="s">
+      <c r="A3" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" s="29" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5264,41 +5195,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>185</v>
+      <c r="A3" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>18450</v>
@@ -5316,17 +5247,17 @@
       <c r="G4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="28" t="n">
+      <c r="H4" s="30" t="n">
         <f aca="false">IFERROR(E4/D4,0)</f>
         <v>0.220650406504065</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>24600</v>
@@ -5344,17 +5275,17 @@
       <c r="G5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="28" t="n">
+      <c r="H5" s="30" t="n">
         <f aca="false">IFERROR(E5/D5,0)</f>
         <v>0.619308943089431</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0</v>
@@ -5372,17 +5303,17 @@
       <c r="G6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="28" t="n">
+      <c r="H6" s="30" t="n">
         <f aca="false">IFERROR(E6/D6,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>0</v>
@@ -5400,17 +5331,17 @@
       <c r="G7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="28" t="n">
+      <c r="H7" s="30" t="n">
         <f aca="false">IFERROR(E7/D7,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>0</v>
@@ -5428,17 +5359,17 @@
       <c r="G8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="H8" s="30" t="n">
         <f aca="false">IFERROR(E8/D8,0)</f>
         <v>0.992592592592593</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>96801</v>
@@ -5456,17 +5387,17 @@
       <c r="G9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="28" t="n">
+      <c r="H9" s="30" t="n">
         <f aca="false">IFERROR(E9/D9,0)</f>
         <v>0.572930548238138</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>454876</v>
@@ -5484,17 +5415,17 @@
       <c r="G10" s="6" t="n">
         <v>8449.81</v>
       </c>
-      <c r="H10" s="28" t="n">
+      <c r="H10" s="30" t="n">
         <f aca="false">IFERROR(E10/D10,0)</f>
         <v>1.02093385889781</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>835857</v>
@@ -5512,17 +5443,17 @@
       <c r="G11" s="6" t="n">
         <v>95810.87</v>
       </c>
-      <c r="H11" s="28" t="n">
+      <c r="H11" s="30" t="n">
         <f aca="false">IFERROR(E11/D11,0)</f>
         <v>0.741450646284461</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
@@ -5540,17 +5471,17 @@
       <c r="G12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="28" t="n">
+      <c r="H12" s="30" t="n">
         <f aca="false">IFERROR(E12/D12,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>0</v>
@@ -5568,17 +5499,17 @@
       <c r="G13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="28" t="n">
+      <c r="H13" s="30" t="n">
         <f aca="false">IFERROR(E13/D13,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>0</v>
@@ -5596,17 +5527,17 @@
       <c r="G14" s="6" t="n">
         <v>2517.35</v>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="H14" s="30" t="n">
         <f aca="false">IFERROR(E14/D14,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>26000</v>
@@ -5624,17 +5555,17 @@
       <c r="G15" s="6" t="n">
         <v>1334.68</v>
       </c>
-      <c r="H15" s="28" t="n">
+      <c r="H15" s="30" t="n">
         <f aca="false">IFERROR(E15/D15,0)</f>
         <v>0.0926876923076923</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>5850</v>
@@ -5652,17 +5583,17 @@
       <c r="G16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="28" t="n">
+      <c r="H16" s="30" t="n">
         <f aca="false">IFERROR(E16/D16,0)</f>
         <v>3.81538461538462</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>0</v>
@@ -5680,17 +5611,17 @@
       <c r="G17" s="6" t="n">
         <v>262.14</v>
       </c>
-      <c r="H17" s="28" t="n">
+      <c r="H17" s="30" t="n">
         <f aca="false">IFERROR(E17/D17,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>102758</v>
@@ -5708,17 +5639,17 @@
       <c r="G18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="28" t="n">
+      <c r="H18" s="30" t="n">
         <f aca="false">IFERROR(E18/D18,0)</f>
         <v>0.382528854201133</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>12450</v>
@@ -5736,17 +5667,17 @@
       <c r="G19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="28" t="n">
+      <c r="H19" s="30" t="n">
         <f aca="false">IFERROR(E19/D19,0)</f>
         <v>0.442971887550201</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>444827.57</v>
@@ -5764,17 +5695,17 @@
       <c r="G20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="28" t="n">
+      <c r="H20" s="30" t="n">
         <f aca="false">IFERROR(E20/D20,0)</f>
         <v>0.956015267777114</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>89668.8</v>
@@ -5792,14 +5723,14 @@
       <c r="G21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="28" t="n">
+      <c r="H21" s="30" t="n">
         <f aca="false">IFERROR(E21/D21,0)</f>
         <v>0.817464551667349</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="27" t="s">
-        <v>222</v>
+      <c r="A22" s="17" t="s">
+        <v>227</v>
       </c>
       <c r="C22" s="7" t="n">
         <f aca="false">SUM(C4:C21)</f>
@@ -5852,32 +5783,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>185</v>
+      <c r="A3" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="27" t="s">
-        <v>227</v>
+      <c r="A4" s="17" t="s">
+        <v>232</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>4</v>
@@ -5892,14 +5823,14 @@
         <f aca="false">C4-D4</f>
         <v>23729.75</v>
       </c>
-      <c r="F4" s="28" t="n">
+      <c r="F4" s="30" t="n">
         <f aca="false">IFERROR(D4/C4,0)</f>
         <v>0.448786295005807</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
-        <v>228</v>
+      <c r="A5" s="17" t="s">
+        <v>233</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>6</v>
@@ -5914,14 +5845,14 @@
         <f aca="false">C5-D5</f>
         <v>246079.55</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="30" t="n">
         <f aca="false">IFERROR(D5/C5,0)</f>
         <v>0.823004717629145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="s">
-        <v>229</v>
+      <c r="A6" s="17" t="s">
+        <v>234</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>5</v>
@@ -5936,14 +5867,14 @@
         <f aca="false">C6-D6</f>
         <v>75032.77</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="30" t="n">
         <f aca="false">IFERROR(D6/C6,0)</f>
         <v>0.489774306736118</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="s">
-        <v>230</v>
+      <c r="A7" s="17" t="s">
+        <v>235</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>2</v>
@@ -5958,16 +5889,16 @@
         <f aca="false">C7-D7</f>
         <v>36227.1</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="30" t="n">
         <f aca="false">IFERROR(D7/C7,0)</f>
         <v>0.932771767805718</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="B8" s="29" t="n">
+      <c r="A8" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="31" t="n">
         <f aca="false">SUM(B4:B7)</f>
         <v>17</v>
       </c>
@@ -6016,43 +5947,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="30" t="s">
-        <v>232</v>
+      <c r="A2" s="32" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="G4" s="26" t="s">
+      <c r="A4" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="G4" s="29" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>18450</v>
@@ -6064,21 +5995,21 @@
         <f aca="false">C5-D5</f>
         <v>14379</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="30" t="n">
         <f aca="false">IFERROR((D5-C5)/C5,0)</f>
         <v>-0.779349593495935</v>
       </c>
-      <c r="G5" s="31" t="str">
+      <c r="G5" s="33" t="str">
         <f aca="false">IF(C5=0,"UNBUDGETED",IF(F5&gt;0.5,"CRITICAL",IF(F5&gt;0.1,"OVER",IF(F5&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>24600</v>
@@ -6090,21 +6021,21 @@
         <f aca="false">C6-D6</f>
         <v>9365</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="30" t="n">
         <f aca="false">IFERROR((D6-C6)/C6,0)</f>
         <v>-0.380691056910569</v>
       </c>
-      <c r="G6" s="31" t="str">
+      <c r="G6" s="33" t="str">
         <f aca="false">IF(C6=0,"UNBUDGETED",IF(F6&gt;0.5,"CRITICAL",IF(F6&gt;0.1,"OVER",IF(F6&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>0</v>
@@ -6116,21 +6047,21 @@
         <f aca="false">C7-D7</f>
         <v>-14.25</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="30" t="n">
         <f aca="false">IFERROR((D7-C7)/C7,0)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="31" t="str">
+      <c r="G7" s="33" t="str">
         <f aca="false">IF(C7=0,"UNBUDGETED",IF(F7&gt;0.5,"CRITICAL",IF(F7&gt;0.1,"OVER",IF(F7&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>675</v>
@@ -6142,21 +6073,21 @@
         <f aca="false">C8-D8</f>
         <v>5</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="30" t="n">
         <f aca="false">IFERROR((D8-C8)/C8,0)</f>
         <v>-0.00740740740740741</v>
       </c>
-      <c r="G8" s="31" t="str">
+      <c r="G8" s="33" t="str">
         <f aca="false">IF(C8=0,"UNBUDGETED",IF(F8&gt;0.5,"CRITICAL",IF(F8&gt;0.1,"OVER",IF(F8&lt;-0.1,"UNDER","ON"))))</f>
         <v>ON</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>96801</v>
@@ -6168,21 +6099,21 @@
         <f aca="false">C9-D9</f>
         <v>41340.75</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="30" t="n">
         <f aca="false">IFERROR((D9-C9)/C9,0)</f>
         <v>-0.427069451761862</v>
       </c>
-      <c r="G9" s="31" t="str">
+      <c r="G9" s="33" t="str">
         <f aca="false">IF(C9=0,"UNBUDGETED",IF(F9&gt;0.5,"CRITICAL",IF(F9&gt;0.1,"OVER",IF(F9&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>454876</v>
@@ -6194,21 +6125,21 @@
         <f aca="false">C10-D10</f>
         <v>-9522.31</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="30" t="n">
         <f aca="false">IFERROR((D10-C10)/C10,0)</f>
         <v>0.0209338588978095</v>
       </c>
-      <c r="G10" s="31" t="str">
+      <c r="G10" s="33" t="str">
         <f aca="false">IF(C10=0,"UNBUDGETED",IF(F10&gt;0.5,"CRITICAL",IF(F10&gt;0.1,"OVER",IF(F10&lt;-0.1,"UNDER","ON"))))</f>
         <v>ON</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>838640</v>
@@ -6220,21 +6151,21 @@
         <f aca="false">C11-D11</f>
         <v>216829.83</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="30" t="n">
         <f aca="false">IFERROR((D11-C11)/C11,0)</f>
         <v>-0.258549353715539</v>
       </c>
-      <c r="G11" s="31" t="str">
+      <c r="G11" s="33" t="str">
         <f aca="false">IF(C11=0,"UNBUDGETED",IF(F11&gt;0.5,"CRITICAL",IF(F11&gt;0.1,"OVER",IF(F11&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
@@ -6246,21 +6177,21 @@
         <f aca="false">C12-D12</f>
         <v>-2568.72</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="30" t="n">
         <f aca="false">IFERROR((D12-C12)/C12,0)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="31" t="str">
+      <c r="G12" s="33" t="str">
         <f aca="false">IF(C12=0,"UNBUDGETED",IF(F12&gt;0.5,"CRITICAL",IF(F12&gt;0.1,"OVER",IF(F12&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>26000</v>
@@ -6272,21 +6203,21 @@
         <f aca="false">C13-D13</f>
         <v>23590.12</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="30" t="n">
         <f aca="false">IFERROR((D13-C13)/C13,0)</f>
         <v>-0.907312307692308</v>
       </c>
-      <c r="G13" s="31" t="str">
+      <c r="G13" s="33" t="str">
         <f aca="false">IF(C13=0,"UNBUDGETED",IF(F13&gt;0.5,"CRITICAL",IF(F13&gt;0.1,"OVER",IF(F13&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>5850</v>
@@ -6298,21 +6229,21 @@
         <f aca="false">C14-D14</f>
         <v>-16470</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="30" t="n">
         <f aca="false">IFERROR((D14-C14)/C14,0)</f>
         <v>2.81538461538462</v>
       </c>
-      <c r="G14" s="31" t="str">
+      <c r="G14" s="33" t="str">
         <f aca="false">IF(C14=0,"UNBUDGETED",IF(F14&gt;0.5,"CRITICAL",IF(F14&gt;0.1,"OVER",IF(F14&lt;-0.1,"UNDER","ON"))))</f>
         <v>CRITICAL</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>0</v>
@@ -6324,21 +6255,21 @@
         <f aca="false">C15-D15</f>
         <v>-2472.45</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="30" t="n">
         <f aca="false">IFERROR((D15-C15)/C15,0)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="31" t="str">
+      <c r="G15" s="33" t="str">
         <f aca="false">IF(C15=0,"UNBUDGETED",IF(F15&gt;0.5,"CRITICAL",IF(F15&gt;0.1,"OVER",IF(F15&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>102758</v>
@@ -6350,21 +6281,21 @@
         <f aca="false">C16-D16</f>
         <v>63450.1</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="30" t="n">
         <f aca="false">IFERROR((D16-C16)/C16,0)</f>
         <v>-0.617471145798867</v>
       </c>
-      <c r="G16" s="31" t="str">
+      <c r="G16" s="33" t="str">
         <f aca="false">IF(C16=0,"UNBUDGETED",IF(F16&gt;0.5,"CRITICAL",IF(F16&gt;0.1,"OVER",IF(F16&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>12450</v>
@@ -6376,21 +6307,21 @@
         <f aca="false">C17-D17</f>
         <v>6935</v>
       </c>
-      <c r="F17" s="28" t="n">
+      <c r="F17" s="30" t="n">
         <f aca="false">IFERROR((D17-C17)/C17,0)</f>
         <v>-0.557028112449799</v>
       </c>
-      <c r="G17" s="31" t="str">
+      <c r="G17" s="33" t="str">
         <f aca="false">IF(C17=0,"UNBUDGETED",IF(F17&gt;0.5,"CRITICAL",IF(F17&gt;0.1,"OVER",IF(F17&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>448466.07</v>
@@ -6402,21 +6333,21 @@
         <f aca="false">C18-D18</f>
         <v>19725.66</v>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="F18" s="30" t="n">
         <f aca="false">IFERROR((D18-C18)/C18,0)</f>
         <v>-0.043984732222886</v>
       </c>
-      <c r="G18" s="31" t="str">
+      <c r="G18" s="33" t="str">
         <f aca="false">IF(C18=0,"UNBUDGETED",IF(F18&gt;0.5,"CRITICAL",IF(F18&gt;0.1,"OVER",IF(F18&lt;-0.1,"UNDER","ON"))))</f>
         <v>ON</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>90401.29</v>
@@ -6428,11 +6359,11 @@
         <f aca="false">C19-D19</f>
         <v>16501.44</v>
       </c>
-      <c r="F19" s="28" t="n">
+      <c r="F19" s="30" t="n">
         <f aca="false">IFERROR((D19-C19)/C19,0)</f>
         <v>-0.182535448332651</v>
       </c>
-      <c r="G19" s="31" t="str">
+      <c r="G19" s="33" t="str">
         <f aca="false">IF(C19=0,"UNBUDGETED",IF(F19&gt;0.5,"CRITICAL",IF(F19&gt;0.1,"OVER",IF(F19&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
@@ -6464,26 +6395,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>238</v>
+      <c r="A3" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>500869.06</v>
@@ -6491,14 +6422,14 @@
       <c r="C4" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="30" t="n">
         <f aca="false">IFERROR(B4/SUM(B$4:B$16),0)</f>
         <v>0.467237248122204</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>305149.79</v>
@@ -6506,14 +6437,14 @@
       <c r="C5" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="30" t="n">
         <f aca="false">IFERROR(B5/SUM(B$4:B$16),0)</f>
         <v>0.284659923183653</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>103987.31</v>
@@ -6521,14 +6452,14 @@
       <c r="C6" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="30" t="n">
         <f aca="false">IFERROR(B6/SUM(B$4:B$16),0)</f>
         <v>0.0970048830008197</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>76546</v>
@@ -6536,14 +6467,14 @@
       <c r="C7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="30" t="n">
         <f aca="false">IFERROR(B7/SUM(B$4:B$16),0)</f>
         <v>0.071406172293338</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>52035.97</v>
@@ -6551,14 +6482,14 @@
       <c r="C8" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="30" t="n">
         <f aca="false">IFERROR(B8/SUM(B$4:B$16),0)</f>
         <v>0.0485419151787287</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>22320</v>
@@ -6566,14 +6497,14 @@
       <c r="C9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="30" t="n">
         <f aca="false">IFERROR(B9/SUM(B$4:B$16),0)</f>
         <v>0.0208212808714669</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>2472.45</v>
@@ -6581,14 +6512,14 @@
       <c r="C10" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D10" s="30" t="n">
         <f aca="false">IFERROR(B10/SUM(B$4:B$16),0)</f>
         <v>0.00230643261158863</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>2408</v>
@@ -6596,14 +6527,14 @@
       <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="30" t="n">
         <f aca="false">IFERROR(B11/SUM(B$4:B$16),0)</f>
         <v>0.00224631023021919</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B12" s="6" t="n">
         <v>1983.84</v>
@@ -6611,14 +6542,14 @@
       <c r="C12" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="30" t="n">
         <f aca="false">IFERROR(B12/SUM(B$4:B$16),0)</f>
         <v>0.00185063126541446</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B13" s="6" t="n">
         <v>1865.27</v>
@@ -6626,14 +6557,14 @@
       <c r="C13" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="28" t="n">
+      <c r="D13" s="30" t="n">
         <f aca="false">IFERROR(B13/SUM(B$4:B$16),0)</f>
         <v>0.00174002287505023</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>1602.9</v>
@@ -6641,14 +6572,14 @@
       <c r="C14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="28" t="n">
+      <c r="D14" s="30" t="n">
         <f aca="false">IFERROR(B14/SUM(B$4:B$16),0)</f>
         <v>0.00149527021097107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B15" s="6" t="n">
         <v>544.61</v>
@@ -6656,14 +6587,14 @@
       <c r="C15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="30" t="n">
         <f aca="false">IFERROR(B15/SUM(B$4:B$16),0)</f>
         <v>0.000508041118969963</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B16" s="6" t="n">
         <v>194.96</v>
@@ -6671,20 +6602,20 @@
       <c r="C16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D16" s="30" t="n">
         <f aca="false">IFERROR(B16/SUM(B$4:B$16),0)</f>
         <v>0.000181869037576218</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="s">
-        <v>252</v>
+      <c r="A17" s="17" t="s">
+        <v>257</v>
       </c>
       <c r="B17" s="7" t="n">
         <f aca="false">SUM(B4:B16)</f>
         <v>1071980.16</v>
       </c>
-      <c r="C17" s="32" t="n">
+      <c r="C17" s="34" t="n">
         <f aca="false">SUM(C4:C16)</f>
         <v>436</v>
       </c>

--- a/owp/owp-2109-live/cortex output files/OWP_2109_JCR_Cortex_v2.xlsx
+++ b/owp/owp-2109-live/cortex output files/OWP_2109_JCR_Cortex_v2.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="404">
   <si>
     <t xml:space="preserve">OWP #2109 · Marysville Ph2</t>
   </si>
@@ -320,13 +320,13 @@
     <t xml:space="preserve">Plumbing Units</t>
   </si>
   <si>
-    <t xml:space="preserve">246  ⚠ UNVERIFIED ESTIMATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Units provenance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠ UNVERIFIED ESTIMATE — set by prior session in parse_2109.py PROJECT_META. JDR has no unit count. No GDrive folder mounted. Must be confirmed against drawing P001 or OWP bid sheet once available. (Phase 1 = #2097 Intracorp Marysville — Job Book folder exists but is empty.)</t>
+    <t xml:space="preserve">246  ✓ CONFIRMED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Units source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✓ CONFIRMED via OWP Project List with Schedule (04-01-26 master tracker). 4 corroborating entries: Schedule rows 95 &amp; 184, Projects Bid rows 340 (Oct 11 2024 bid · $4.57M) + 353 (Jan 7 2025 bid · $3.70M — matches contract_original). Phase 1 = Job #2097 (228 units · $5.14M); combined Marysville site = 228 + 246 = 474 units total.</t>
   </si>
   <si>
     <t xml:space="preserve">Total Fixtures</t>
@@ -374,9 +374,6 @@
     <t xml:space="preserve">OWP Estimator (takeoff)</t>
   </si>
   <si>
-    <t xml:space="preserve">30 workers · 377 hrs logged YTD</t>
-  </si>
-  <si>
     <t xml:space="preserve">PROJECT TEAM — OWNER &amp; DEVELOPMENT</t>
   </si>
   <si>
@@ -392,9 +389,15 @@
     <t xml:space="preserve">Architect</t>
   </si>
   <si>
+    <t xml:space="preserve">Intracorp (in-house)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Structural Engineer</t>
   </si>
   <si>
+    <t xml:space="preserve">BCRA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Civil Engineer</t>
   </si>
   <si>
@@ -425,9 +428,6 @@
     <t xml:space="preserve">Concentration Note</t>
   </si>
   <si>
-    <t xml:space="preserve">Pacific Plumbing 46.7% + Consolidated 28.5% + Rosen 9.7% = Top 3 dominate at 84.9% of AP. Standard for OWP active jobs.</t>
-  </si>
-  <si>
     <t xml:space="preserve">DOCUMENT META (current)</t>
   </si>
   <si>
@@ -464,9 +464,6 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Project is in active Roughin. Documents flow has begun but the GDrive folder for this job hasn't been wired to the dashboard yet — once mounted, the document counts will populate.</t>
-  </si>
-  <si>
     <t xml:space="preserve">DATA SOURCES</t>
   </si>
   <si>
@@ -497,9 +494,6 @@
     <t xml:space="preserve">GDrive Status</t>
   </si>
   <si>
-    <t xml:space="preserve">GDrive folder not yet wired to local mount. Team data from index.html PROJECT_TEAMS['2109'] + JDR identity block.</t>
-  </si>
-  <si>
     <t xml:space="preserve">RISK FLAGS / ACTIONS</t>
   </si>
   <si>
@@ -527,6 +521,63 @@
     <t xml:space="preserve">$153,880 held · 4.3% of billed. Track release schedule once project nears closeout.</t>
   </si>
   <si>
+    <t xml:space="preserve">BID HISTORY (from OWP Project List)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bid Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Bid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dec 16 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$10,422,514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BID — combined Ph1+Ph2 · 474u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jun 30 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$10,609,805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BID — combined revised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct  6 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$10,503,592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 11 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$4,574,995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BID — Ph2 split out · 246u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan  7 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BID — Ph2 final · matches contract</t>
+  </si>
+  <si>
     <t xml:space="preserve">Contract Summary</t>
   </si>
   <si>
@@ -1169,9 +1220,6 @@
     <t xml:space="preserve">Version</t>
   </si>
   <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-04-25</t>
   </si>
   <si>
@@ -1194,6 +1242,12 @@
   </si>
   <si>
     <t xml:space="preserve">Audited unit/fixture counts. Units 246 flagged as UNVERIFIED ESTIMATE (no source-doc verification possible — JDR has no unit count, no GDrive folder mounted). Fixtures marked UNKNOWN.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1.3 · units CONFIRMED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified units 246 against OWP master tracker (OWP Project List with Schedule - UPDATED 04-01-26.xlsx). 4 corroborating entries found across Schedule + Projects Bid tabs. UNVERIFIED flag removed. Architect (Intracorp (in-house)), MEP (BCRA), Owner (Intracorp (owner-GC)) all backfilled from the same source. Added BID HISTORY section to Job Info tab.</t>
   </si>
 </sst>
 </file>
@@ -1389,14 +1443,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-        <bgColor rgb="FFFFF8E7"/>
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor rgb="FFD1ECF1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor rgb="FFD1ECF1"/>
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFF8E7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1500,7 +1554,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1585,11 +1639,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1597,7 +1651,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1615,6 +1677,22 @@
     </xf>
     <xf numFmtId="164" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1681,7 +1759,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1689,7 +1767,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1705,15 +1783,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2414,564 +2488,564 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>260</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>263</v>
+      <c r="A3" s="35" t="s">
+        <v>276</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>279</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B4" s="35" t="n">
+        <v>281</v>
+      </c>
+      <c r="B4" s="41" t="n">
         <v>168</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>11592</v>
       </c>
-      <c r="D4" s="36" t="n">
+      <c r="D4" s="42" t="n">
         <f aca="false">IFERROR(C4/B4,0)</f>
         <v>69</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B5" s="35" t="n">
+        <v>283</v>
+      </c>
+      <c r="B5" s="41" t="n">
         <v>98</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>5831</v>
       </c>
-      <c r="D5" s="36" t="n">
+      <c r="D5" s="42" t="n">
         <f aca="false">IFERROR(C5/B5,0)</f>
         <v>59.5</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="35" t="n">
+        <v>284</v>
+      </c>
+      <c r="B6" s="41" t="n">
         <v>60</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="36" t="n">
+      <c r="D6" s="42" t="n">
         <f aca="false">IFERROR(C6/B6,0)</f>
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="B7" s="35" t="n">
+        <v>286</v>
+      </c>
+      <c r="B7" s="41" t="n">
         <v>28.8</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1553</v>
       </c>
-      <c r="D7" s="36" t="n">
+      <c r="D7" s="42" t="n">
         <f aca="false">IFERROR(C7/B7,0)</f>
         <v>53.9236111111111</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="B8" s="35" t="n">
+        <v>287</v>
+      </c>
+      <c r="B8" s="41" t="n">
         <v>11</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>572</v>
       </c>
-      <c r="D8" s="36" t="n">
+      <c r="D8" s="42" t="n">
         <f aca="false">IFERROR(C8/B8,0)</f>
         <v>52</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B9" s="35" t="n">
+        <v>288</v>
+      </c>
+      <c r="B9" s="41" t="n">
         <v>8.5</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>238</v>
       </c>
-      <c r="D9" s="36" t="n">
+      <c r="D9" s="42" t="n">
         <f aca="false">IFERROR(C9/B9,0)</f>
         <v>28</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="B10" s="35" t="n">
+        <v>290</v>
+      </c>
+      <c r="B10" s="41" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>204</v>
       </c>
-      <c r="D10" s="36" t="n">
+      <c r="D10" s="42" t="n">
         <f aca="false">IFERROR(C10/B10,0)</f>
         <v>68</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="B11" s="35" t="n">
+        <v>291</v>
+      </c>
+      <c r="B11" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="36" t="n">
+      <c r="D11" s="42" t="n">
         <f aca="false">IFERROR(C11/B11,0)</f>
         <v>0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="B12" s="35" t="n">
+        <v>293</v>
+      </c>
+      <c r="B12" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="36" t="n">
+      <c r="D12" s="42" t="n">
         <f aca="false">IFERROR(C12/B12,0)</f>
         <v>0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="B13" s="35" t="n">
+        <v>294</v>
+      </c>
+      <c r="B13" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="36" t="n">
+      <c r="D13" s="42" t="n">
         <f aca="false">IFERROR(C13/B13,0)</f>
         <v>0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B14" s="35" t="n">
+        <v>295</v>
+      </c>
+      <c r="B14" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="36" t="n">
+      <c r="D14" s="42" t="n">
         <f aca="false">IFERROR(C14/B14,0)</f>
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="B15" s="35" t="n">
+        <v>296</v>
+      </c>
+      <c r="B15" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="36" t="n">
+      <c r="D15" s="42" t="n">
         <f aca="false">IFERROR(C15/B15,0)</f>
         <v>0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="B16" s="35" t="n">
+        <v>297</v>
+      </c>
+      <c r="B16" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="36" t="n">
+      <c r="D16" s="42" t="n">
         <f aca="false">IFERROR(C16/B16,0)</f>
         <v>0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="B17" s="35" t="n">
+        <v>298</v>
+      </c>
+      <c r="B17" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="36" t="n">
+      <c r="D17" s="42" t="n">
         <f aca="false">IFERROR(C17/B17,0)</f>
         <v>0</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="B18" s="35" t="n">
+        <v>299</v>
+      </c>
+      <c r="B18" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="36" t="n">
+      <c r="D18" s="42" t="n">
         <f aca="false">IFERROR(C18/B18,0)</f>
         <v>0</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="B19" s="35" t="n">
+        <v>300</v>
+      </c>
+      <c r="B19" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="36" t="n">
+      <c r="D19" s="42" t="n">
         <f aca="false">IFERROR(C19/B19,0)</f>
         <v>0</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="B20" s="35" t="n">
+        <v>301</v>
+      </c>
+      <c r="B20" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="36" t="n">
+      <c r="D20" s="42" t="n">
         <f aca="false">IFERROR(C20/B20,0)</f>
         <v>0</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="B21" s="35" t="n">
+        <v>302</v>
+      </c>
+      <c r="B21" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="36" t="n">
+      <c r="D21" s="42" t="n">
         <f aca="false">IFERROR(C21/B21,0)</f>
         <v>0</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="B22" s="35" t="n">
+        <v>303</v>
+      </c>
+      <c r="B22" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="36" t="n">
+      <c r="D22" s="42" t="n">
         <f aca="false">IFERROR(C22/B22,0)</f>
         <v>0</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B23" s="35" t="n">
+        <v>304</v>
+      </c>
+      <c r="B23" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="36" t="n">
+      <c r="D23" s="42" t="n">
         <f aca="false">IFERROR(C23/B23,0)</f>
         <v>0</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="B24" s="35" t="n">
+        <v>305</v>
+      </c>
+      <c r="B24" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="36" t="n">
+      <c r="D24" s="42" t="n">
         <f aca="false">IFERROR(C24/B24,0)</f>
         <v>0</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="B25" s="35" t="n">
+        <v>306</v>
+      </c>
+      <c r="B25" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="36" t="n">
+      <c r="D25" s="42" t="n">
         <f aca="false">IFERROR(C25/B25,0)</f>
         <v>0</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="B26" s="35" t="n">
+        <v>307</v>
+      </c>
+      <c r="B26" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="36" t="n">
+      <c r="D26" s="42" t="n">
         <f aca="false">IFERROR(C26/B26,0)</f>
         <v>0</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="B27" s="35" t="n">
+        <v>308</v>
+      </c>
+      <c r="B27" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="36" t="n">
+      <c r="D27" s="42" t="n">
         <f aca="false">IFERROR(C27/B27,0)</f>
         <v>0</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B28" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="42" t="n">
+        <f aca="false">IFERROR(C28/B28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>292</v>
-      </c>
-      <c r="B28" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="36" t="n">
-        <f aca="false">IFERROR(C28/B28,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="B29" s="35" t="n">
+        <v>310</v>
+      </c>
+      <c r="B29" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="36" t="n">
+      <c r="D29" s="42" t="n">
         <f aca="false">IFERROR(C29/B29,0)</f>
         <v>0</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="B30" s="35" t="n">
+        <v>311</v>
+      </c>
+      <c r="B30" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="36" t="n">
+      <c r="D30" s="42" t="n">
         <f aca="false">IFERROR(C30/B30,0)</f>
         <v>0</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="B31" s="35" t="n">
+        <v>312</v>
+      </c>
+      <c r="B31" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="36" t="n">
+      <c r="D31" s="42" t="n">
         <f aca="false">IFERROR(C31/B31,0)</f>
         <v>0</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="B32" s="35" t="n">
+        <v>313</v>
+      </c>
+      <c r="B32" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="36" t="n">
+      <c r="D32" s="42" t="n">
         <f aca="false">IFERROR(C32/B32,0)</f>
         <v>0</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="B33" s="35" t="n">
+        <v>314</v>
+      </c>
+      <c r="B33" s="41" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="36" t="n">
+      <c r="D33" s="42" t="n">
         <f aca="false">IFERROR(C33/B33,0)</f>
         <v>0</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -3001,94 +3075,94 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
-        <v>263</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>299</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>260</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>300</v>
+      <c r="A3" s="35" t="s">
+        <v>280</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>316</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="41" t="n">
         <v>308.8</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>19752</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="36" t="n">
         <f aca="false">IFERROR(C4/SUM(C$4:C$7),0)</f>
         <v>0.818446859263186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="41" t="n">
         <v>8.5</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>238</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="36" t="n">
         <f aca="false">IFERROR(C5/SUM(C$4:C$7),0)</f>
         <v>0.022528491916247</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="41" t="n">
         <v>60</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="36" t="n">
         <f aca="false">IFERROR(C6/SUM(C$4:C$7),0)</f>
         <v>0.159024648820567</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="41" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="36" t="n">
         <f aca="false">IFERROR(C7/SUM(C$4:C$7),0)</f>
         <v>0</v>
       </c>
@@ -3118,38 +3192,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B3" s="35" t="n">
+        <v>319</v>
+      </c>
+      <c r="B3" s="41" t="n">
         <v>377</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="B4" s="37" t="n">
+        <v>320</v>
+      </c>
+      <c r="B4" s="43" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="B5" s="35" t="n">
+        <v>321</v>
+      </c>
+      <c r="B5" s="41" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B6" s="38" t="n">
+        <v>322</v>
+      </c>
+      <c r="B6" s="44" t="n">
         <v>9463.25</v>
       </c>
     </row>
@@ -3157,7 +3231,7 @@
       <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="39" t="n">
+      <c r="B7" s="45" t="n">
         <v>0.959977154233929</v>
       </c>
     </row>
@@ -3186,79 +3260,79 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
-        <v>307</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>308</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>167</v>
+      <c r="A3" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>326</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B4" s="39" t="n">
+        <v>327</v>
+      </c>
+      <c r="B4" s="45" t="n">
         <v>0.429940226161253</v>
       </c>
-      <c r="C4" s="39" t="n">
+      <c r="C4" s="45" t="n">
         <v>0.34</v>
       </c>
-      <c r="D4" s="30" t="n">
+      <c r="D4" s="36" t="n">
         <f aca="false">B4-C4</f>
         <v>0.089940226161253</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="B5" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="39" t="n">
+        <v>328</v>
+      </c>
+      <c r="B5" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="45" t="n">
         <v>0.45</v>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="36" t="n">
         <f aca="false">B5-C5</f>
         <v>-0.45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="B6" s="39" t="n">
+        <v>329</v>
+      </c>
+      <c r="B6" s="45" t="n">
         <v>0.467237248122204</v>
       </c>
-      <c r="C6" s="39" t="n">
+      <c r="C6" s="45" t="n">
         <v>0.38</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="36" t="n">
         <f aca="false">B6-C6</f>
         <v>0.087237248122204</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="B7" s="35" t="n">
+        <v>330</v>
+      </c>
+      <c r="B7" s="41" t="n">
         <v>1.53353658536585</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="41" t="n">
         <v>95</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="46" t="n">
         <f aca="false">B7-C7</f>
         <v>-93.4664634146342</v>
       </c>
@@ -3290,8 +3364,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
-        <v>314</v>
+      <c r="A1" s="47" t="s">
+        <v>331</v>
       </c>
       <c r="F1" s="1"/>
     </row>
@@ -3299,236 +3373,236 @@
       <c r="F2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="42" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>315</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>317</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>318</v>
+      <c r="A3" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>332</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>333</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>334</v>
+      </c>
+      <c r="E3" s="48" t="s">
+        <v>335</v>
       </c>
       <c r="F3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="n">
+      <c r="A4" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="44" t="s">
-        <v>319</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>320</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>321</v>
-      </c>
-      <c r="E4" s="45" t="s">
-        <v>322</v>
+      <c r="B4" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>337</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>338</v>
+      </c>
+      <c r="E4" s="51" t="s">
+        <v>339</v>
       </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="43" t="n">
+      <c r="A5" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="44" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>324</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>325</v>
-      </c>
-      <c r="E5" s="45" t="s">
-        <v>322</v>
+      <c r="B5" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>341</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>342</v>
+      </c>
+      <c r="E5" s="51" t="s">
+        <v>339</v>
       </c>
       <c r="F5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="n">
+      <c r="A6" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="44" t="s">
-        <v>326</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>324</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>327</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>322</v>
+      <c r="B6" s="50" t="s">
+        <v>343</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>341</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="E6" s="51" t="s">
+        <v>339</v>
       </c>
       <c r="F6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="n">
+      <c r="A7" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="43" t="s">
-        <v>328</v>
-      </c>
-      <c r="E7" s="45" t="s">
-        <v>322</v>
+      <c r="D7" s="49" t="s">
+        <v>345</v>
+      </c>
+      <c r="E7" s="51" t="s">
+        <v>339</v>
       </c>
       <c r="F7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="n">
+      <c r="A8" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="43" t="s">
-        <v>329</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>330</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>322</v>
+      <c r="C8" s="49" t="s">
+        <v>346</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>347</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>339</v>
       </c>
       <c r="F8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="n">
+      <c r="A9" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="43" t="s">
-        <v>331</v>
-      </c>
-      <c r="C9" s="43" t="s">
+      <c r="B9" s="49" t="s">
+        <v>348</v>
+      </c>
+      <c r="C9" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="43" t="s">
-        <v>332</v>
-      </c>
-      <c r="E9" s="45" t="s">
-        <v>322</v>
+      <c r="D9" s="49" t="s">
+        <v>349</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>339</v>
       </c>
       <c r="F9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="43" t="n">
+      <c r="A10" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="43" t="s">
-        <v>333</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>334</v>
+      <c r="D10" s="49" t="s">
+        <v>350</v>
+      </c>
+      <c r="E10" s="52" t="s">
+        <v>351</v>
       </c>
       <c r="F10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="n">
+      <c r="A11" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="43" t="s">
-        <v>335</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>336</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>337</v>
-      </c>
-      <c r="E11" s="47" t="s">
-        <v>338</v>
+      <c r="B11" s="49" t="s">
+        <v>352</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>353</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>354</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>355</v>
       </c>
       <c r="F11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="43" t="n">
+      <c r="A12" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="43" t="s">
-        <v>157</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>339</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>340</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>341</v>
+      <c r="B12" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>356</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>357</v>
+      </c>
+      <c r="E12" s="54" t="s">
+        <v>358</v>
       </c>
       <c r="F12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="43" t="n">
+      <c r="A13" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="43" t="s">
-        <v>342</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>343</v>
-      </c>
-      <c r="D13" s="43" t="s">
-        <v>344</v>
-      </c>
-      <c r="E13" s="46" t="s">
-        <v>334</v>
+      <c r="B13" s="49" t="s">
+        <v>359</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>360</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>361</v>
+      </c>
+      <c r="E13" s="52" t="s">
+        <v>351</v>
       </c>
       <c r="F13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="43" t="n">
+      <c r="A14" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="43" t="s">
-        <v>345</v>
-      </c>
-      <c r="C14" s="43" t="s">
-        <v>346</v>
-      </c>
-      <c r="D14" s="43" t="s">
-        <v>333</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>334</v>
+      <c r="B14" s="49" t="s">
+        <v>362</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>363</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>350</v>
+      </c>
+      <c r="E14" s="52" t="s">
+        <v>351</v>
       </c>
       <c r="F14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="43" t="n">
+      <c r="A15" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="43" t="s">
-        <v>347</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>348</v>
-      </c>
-      <c r="D15" s="43" t="s">
-        <v>349</v>
-      </c>
-      <c r="E15" s="46" t="s">
-        <v>334</v>
+      <c r="B15" s="49" t="s">
+        <v>364</v>
+      </c>
+      <c r="C15" s="49" t="s">
+        <v>365</v>
+      </c>
+      <c r="D15" s="49" t="s">
+        <v>366</v>
+      </c>
+      <c r="E15" s="52" t="s">
+        <v>351</v>
       </c>
       <c r="F15" s="1"/>
     </row>
@@ -3602,26 +3676,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="29" t="s">
-        <v>351</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>352</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>167</v>
+      <c r="B3" s="35" t="s">
+        <v>368</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>369</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>2683501.46</v>
@@ -3636,7 +3710,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>-3570012</v>
@@ -3651,7 +3725,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>1071980.16</v>
@@ -3663,7 +3737,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1468646.78</v>
@@ -3675,7 +3749,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>-349534.48</v>
@@ -3711,84 +3785,84 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
-        <v>307</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>359</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>360</v>
+      <c r="A3" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>376</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="49" t="s">
-        <v>310</v>
-      </c>
-      <c r="B4" s="49" t="s">
-        <v>361</v>
-      </c>
-      <c r="C4" s="49" t="s">
-        <v>362</v>
+      <c r="A4" s="55" t="s">
+        <v>327</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>378</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="49" t="s">
-        <v>361</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>363</v>
+      <c r="B5" s="55" t="s">
+        <v>378</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="49" t="s">
-        <v>364</v>
-      </c>
-      <c r="B6" s="49" t="s">
-        <v>365</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>366</v>
+      <c r="A6" s="55" t="s">
+        <v>381</v>
+      </c>
+      <c r="B6" s="55" t="s">
+        <v>382</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="s">
-        <v>312</v>
-      </c>
-      <c r="B7" s="49" t="s">
-        <v>367</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>368</v>
+      <c r="A7" s="55" t="s">
+        <v>329</v>
+      </c>
+      <c r="B7" s="55" t="s">
+        <v>384</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="s">
-        <v>313</v>
-      </c>
-      <c r="B8" s="49" t="s">
-        <v>369</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>370</v>
+      <c r="A8" s="55" t="s">
+        <v>330</v>
+      </c>
+      <c r="B8" s="55" t="s">
+        <v>386</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="s">
-        <v>371</v>
-      </c>
-      <c r="B9" s="49" t="s">
-        <v>372</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>373</v>
+      <c r="A9" s="55" t="s">
+        <v>388</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>389</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -3807,7 +3881,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -3817,51 +3891,62 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
-        <v>375</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>376</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>377</v>
+      <c r="A3" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>393</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="s">
-        <v>381</v>
-      </c>
-      <c r="B5" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="C5" s="52" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="53" t="s">
-        <v>381</v>
+      <c r="A5" s="56" t="s">
+        <v>397</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="56" t="s">
+        <v>397</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>384</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>385</v>
+        <v>400</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>402</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -3880,7 +3965,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="32"/>
@@ -4261,391 +4346,379 @@
       <c r="A36" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
     </row>
     <row r="37" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="B37" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
         <v>101</v>
       </c>
       <c r="B38" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B39" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="27" t="s">
+      <c r="B42" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="28" t="s">
+      <c r="A45" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C48" s="27"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="27"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="27"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+      <c r="E50" s="29"/>
+      <c r="F50" s="29"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="28" t="s">
+      <c r="A52" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B54" s="24"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="14" t="s">
+      <c r="B55" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="B55" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="B56" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="28"/>
-      <c r="F56" s="28"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
+        <v>115</v>
+      </c>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="B59" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="29"/>
+      <c r="E59" s="29"/>
+      <c r="F59" s="29"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="27" t="s">
+      <c r="B60" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="29"/>
+      <c r="F60" s="29"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B61" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="B62" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="B62" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="B63" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" s="28"/>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
+      <c r="A63" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="26"/>
-      <c r="F64" s="26"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="B65" s="24"/>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="24"/>
-      <c r="F65" s="24"/>
+        <v>122</v>
+      </c>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="B66" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="C66" s="27"/>
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
+      <c r="B66" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="C66" s="29"/>
+      <c r="D66" s="29"/>
+      <c r="E66" s="29"/>
+      <c r="F66" s="29"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B67" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="29"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="B68" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="C68" s="24"/>
-      <c r="D68" s="24"/>
-      <c r="E68" s="24"/>
-      <c r="F68" s="24"/>
+      <c r="B68" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="B69" s="28" t="s">
+      <c r="A69" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="26"/>
-      <c r="F70" s="26"/>
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="B71" s="24"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="24"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="24"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="26"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="26"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="19" t="s">
@@ -4719,53 +4792,51 @@
       <c r="E77" s="20"/>
       <c r="F77" s="20"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="19" t="s">
         <v>140</v>
       </c>
       <c r="B78" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C78" s="24"/>
-      <c r="D78" s="24"/>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="25" t="s">
+      <c r="A79" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="B79" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="C79" s="25"/>
-      <c r="D79" s="25"/>
-      <c r="E79" s="25"/>
-      <c r="F79" s="25"/>
+      <c r="B79" s="27"/>
+      <c r="C79" s="27"/>
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
+      <c r="B80" s="28"/>
+      <c r="C80" s="28"/>
+      <c r="D80" s="28"/>
+      <c r="E80" s="28"/>
+      <c r="F80" s="28"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="B81" s="24"/>
-      <c r="C81" s="24"/>
-      <c r="D81" s="24"/>
-      <c r="E81" s="24"/>
-      <c r="F81" s="24"/>
+        <v>142</v>
+      </c>
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B82" s="20" t="s">
         <v>144</v>
-      </c>
-      <c r="B82" s="20" t="s">
-        <v>145</v>
       </c>
       <c r="C82" s="20"/>
       <c r="D82" s="20"/>
@@ -4774,10 +4845,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="B83" s="20" t="s">
         <v>146</v>
-      </c>
-      <c r="B83" s="20" t="s">
-        <v>147</v>
       </c>
       <c r="C83" s="20"/>
       <c r="D83" s="20"/>
@@ -4786,107 +4857,222 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B84" s="20" t="s">
         <v>148</v>
-      </c>
-      <c r="B84" s="20" t="s">
-        <v>149</v>
       </c>
       <c r="C84" s="20"/>
       <c r="D84" s="20"/>
       <c r="E84" s="20"/>
       <c r="F84" s="20"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B85" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="B85" s="20" t="s">
+      <c r="C85" s="26"/>
+      <c r="D85" s="26"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="C85" s="24"/>
-      <c r="D85" s="24"/>
-      <c r="E85" s="24"/>
-      <c r="F85" s="24"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="B86" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="C86" s="25"/>
-      <c r="D86" s="25"/>
-      <c r="E86" s="25"/>
-      <c r="F86" s="25"/>
+      <c r="B86" s="27"/>
+      <c r="C86" s="27"/>
+      <c r="D86" s="27"/>
+      <c r="E86" s="27"/>
+      <c r="F86" s="27"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B87" s="26"/>
-      <c r="C87" s="26"/>
-      <c r="D87" s="26"/>
-      <c r="E87" s="26"/>
-      <c r="F87" s="26"/>
+      <c r="B87" s="28"/>
+      <c r="C87" s="28"/>
+      <c r="D87" s="28"/>
+      <c r="E87" s="28"/>
+      <c r="F87" s="28"/>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="B88" s="24"/>
-      <c r="C88" s="24"/>
-      <c r="D88" s="24"/>
-      <c r="E88" s="24"/>
-      <c r="F88" s="24"/>
+        <v>152</v>
+      </c>
+      <c r="B88" s="26"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="26"/>
+      <c r="E88" s="26"/>
+      <c r="F88" s="26"/>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="B89" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="C89" s="27"/>
-      <c r="D89" s="27"/>
-      <c r="E89" s="27"/>
-      <c r="F89" s="27"/>
+        <v>153</v>
+      </c>
+      <c r="B89" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="C89" s="29"/>
+      <c r="D89" s="29"/>
+      <c r="E89" s="29"/>
+      <c r="F89" s="29"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B90" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="C90" s="29"/>
+      <c r="D90" s="29"/>
+      <c r="E90" s="29"/>
+      <c r="F90" s="29"/>
+    </row>
+    <row r="91" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="B90" s="27" t="s">
+      <c r="B91" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="C90" s="27"/>
-      <c r="D90" s="27"/>
-      <c r="E90" s="27"/>
-      <c r="F90" s="27"/>
-    </row>
-    <row r="91" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="14" t="s">
+      <c r="C91" s="26"/>
+      <c r="D91" s="26"/>
+      <c r="E91" s="26"/>
+      <c r="F91" s="26"/>
+    </row>
+    <row r="92" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="B91" s="27" t="s">
+      <c r="B92" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="C91" s="24"/>
-      <c r="D91" s="24"/>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-    </row>
-    <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="14" t="s">
+      <c r="C92" s="26"/>
+      <c r="D92" s="26"/>
+      <c r="E92" s="26"/>
+      <c r="F92" s="26"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="B92" s="27" t="s">
+      <c r="B94" s="31"/>
+      <c r="C94" s="31"/>
+      <c r="D94" s="31"/>
+      <c r="E94" s="31"/>
+      <c r="F94" s="31"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="C92" s="24"/>
-      <c r="D92" s="24"/>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
+      <c r="B95" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="C95" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="D95" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="E95" s="32" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="B96" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C96" s="33" t="n">
+        <v>474</v>
+      </c>
+      <c r="D96" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="E96" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="F96" s="34"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="B97" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C97" s="33" t="n">
+        <v>474</v>
+      </c>
+      <c r="D97" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="E97" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="F97" s="34"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="B98" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98" s="33" t="n">
+        <v>474</v>
+      </c>
+      <c r="D98" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="E98" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="F98" s="34"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="B99" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99" s="33" t="n">
+        <v>246</v>
+      </c>
+      <c r="D99" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="E99" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="F99" s="34"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B100" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100" s="33" t="n">
+        <v>246</v>
+      </c>
+      <c r="D100" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E100" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="F100" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="78">
+  <mergeCells count="84">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
@@ -4965,6 +5151,12 @@
     <mergeCell ref="B88:F88"/>
     <mergeCell ref="B89:F89"/>
     <mergeCell ref="B90:F90"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="E96:F96"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="E100:F100"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4990,26 +5182,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>167</v>
+      <c r="A3" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>3700937</v>
@@ -5024,7 +5216,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>0</v>
@@ -5039,7 +5231,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">SUM(B4:B5)</f>
@@ -5056,18 +5248,18 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>174</v>
+      <c r="A10" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -5095,30 +5287,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>178</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="E3" s="29" t="s">
+      <c r="A3" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="E3" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>181</v>
+      <c r="F3" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -5149,23 +5341,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="E3" s="29" t="s">
+      <c r="A3" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="35" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5195,41 +5387,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="H3" s="29" t="s">
+      <c r="A3" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="35" t="s">
         <v>190</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>205</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>206</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>18450</v>
@@ -5247,17 +5439,17 @@
       <c r="G4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="30" t="n">
+      <c r="H4" s="36" t="n">
         <f aca="false">IFERROR(E4/D4,0)</f>
         <v>0.220650406504065</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>24600</v>
@@ -5275,17 +5467,17 @@
       <c r="G5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="30" t="n">
+      <c r="H5" s="36" t="n">
         <f aca="false">IFERROR(E5/D5,0)</f>
         <v>0.619308943089431</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0</v>
@@ -5303,17 +5495,17 @@
       <c r="G6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="30" t="n">
+      <c r="H6" s="36" t="n">
         <f aca="false">IFERROR(E6/D6,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>0</v>
@@ -5331,17 +5523,17 @@
       <c r="G7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="30" t="n">
+      <c r="H7" s="36" t="n">
         <f aca="false">IFERROR(E7/D7,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>0</v>
@@ -5359,17 +5551,17 @@
       <c r="G8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="30" t="n">
+      <c r="H8" s="36" t="n">
         <f aca="false">IFERROR(E8/D8,0)</f>
         <v>0.992592592592593</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>96801</v>
@@ -5387,17 +5579,17 @@
       <c r="G9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="30" t="n">
+      <c r="H9" s="36" t="n">
         <f aca="false">IFERROR(E9/D9,0)</f>
         <v>0.572930548238138</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>454876</v>
@@ -5415,17 +5607,17 @@
       <c r="G10" s="6" t="n">
         <v>8449.81</v>
       </c>
-      <c r="H10" s="30" t="n">
+      <c r="H10" s="36" t="n">
         <f aca="false">IFERROR(E10/D10,0)</f>
         <v>1.02093385889781</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>835857</v>
@@ -5443,17 +5635,17 @@
       <c r="G11" s="6" t="n">
         <v>95810.87</v>
       </c>
-      <c r="H11" s="30" t="n">
+      <c r="H11" s="36" t="n">
         <f aca="false">IFERROR(E11/D11,0)</f>
         <v>0.741450646284461</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
@@ -5471,17 +5663,17 @@
       <c r="G12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="30" t="n">
+      <c r="H12" s="36" t="n">
         <f aca="false">IFERROR(E12/D12,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>0</v>
@@ -5499,17 +5691,17 @@
       <c r="G13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="30" t="n">
+      <c r="H13" s="36" t="n">
         <f aca="false">IFERROR(E13/D13,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>0</v>
@@ -5527,17 +5719,17 @@
       <c r="G14" s="6" t="n">
         <v>2517.35</v>
       </c>
-      <c r="H14" s="30" t="n">
+      <c r="H14" s="36" t="n">
         <f aca="false">IFERROR(E14/D14,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>26000</v>
@@ -5555,17 +5747,17 @@
       <c r="G15" s="6" t="n">
         <v>1334.68</v>
       </c>
-      <c r="H15" s="30" t="n">
+      <c r="H15" s="36" t="n">
         <f aca="false">IFERROR(E15/D15,0)</f>
         <v>0.0926876923076923</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>5850</v>
@@ -5583,17 +5775,17 @@
       <c r="G16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="30" t="n">
+      <c r="H16" s="36" t="n">
         <f aca="false">IFERROR(E16/D16,0)</f>
         <v>3.81538461538462</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>0</v>
@@ -5611,17 +5803,17 @@
       <c r="G17" s="6" t="n">
         <v>262.14</v>
       </c>
-      <c r="H17" s="30" t="n">
+      <c r="H17" s="36" t="n">
         <f aca="false">IFERROR(E17/D17,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>102758</v>
@@ -5639,17 +5831,17 @@
       <c r="G18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="30" t="n">
+      <c r="H18" s="36" t="n">
         <f aca="false">IFERROR(E18/D18,0)</f>
         <v>0.382528854201133</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>12450</v>
@@ -5667,17 +5859,17 @@
       <c r="G19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="30" t="n">
+      <c r="H19" s="36" t="n">
         <f aca="false">IFERROR(E19/D19,0)</f>
         <v>0.442971887550201</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>444827.57</v>
@@ -5695,17 +5887,17 @@
       <c r="G20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="30" t="n">
+      <c r="H20" s="36" t="n">
         <f aca="false">IFERROR(E20/D20,0)</f>
         <v>0.956015267777114</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>89668.8</v>
@@ -5723,14 +5915,14 @@
       <c r="G21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="30" t="n">
+      <c r="H21" s="36" t="n">
         <f aca="false">IFERROR(E21/D21,0)</f>
         <v>0.817464551667349</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="C22" s="7" t="n">
         <f aca="false">SUM(C4:C21)</f>
@@ -5783,32 +5975,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
-        <v>229</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>230</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>231</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>190</v>
+      <c r="A3" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>205</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>4</v>
@@ -5823,14 +6015,14 @@
         <f aca="false">C4-D4</f>
         <v>23729.75</v>
       </c>
-      <c r="F4" s="30" t="n">
+      <c r="F4" s="36" t="n">
         <f aca="false">IFERROR(D4/C4,0)</f>
         <v>0.448786295005807</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>6</v>
@@ -5845,14 +6037,14 @@
         <f aca="false">C5-D5</f>
         <v>246079.55</v>
       </c>
-      <c r="F5" s="30" t="n">
+      <c r="F5" s="36" t="n">
         <f aca="false">IFERROR(D5/C5,0)</f>
         <v>0.823004717629145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>5</v>
@@ -5867,14 +6059,14 @@
         <f aca="false">C6-D6</f>
         <v>75032.77</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="36" t="n">
         <f aca="false">IFERROR(D6/C6,0)</f>
         <v>0.489774306736118</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>2</v>
@@ -5889,16 +6081,16 @@
         <f aca="false">C7-D7</f>
         <v>36227.1</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="36" t="n">
         <f aca="false">IFERROR(D7/C7,0)</f>
         <v>0.932771767805718</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="B8" s="31" t="n">
+        <v>244</v>
+      </c>
+      <c r="B8" s="37" t="n">
         <f aca="false">SUM(B4:B7)</f>
         <v>17</v>
       </c>
@@ -5947,43 +6139,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="32" t="s">
-        <v>237</v>
+      <c r="A2" s="38" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>238</v>
-      </c>
-      <c r="G4" s="29" t="s">
+      <c r="A4" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>205</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="G4" s="35" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>18450</v>
@@ -5995,21 +6187,21 @@
         <f aca="false">C5-D5</f>
         <v>14379</v>
       </c>
-      <c r="F5" s="30" t="n">
+      <c r="F5" s="36" t="n">
         <f aca="false">IFERROR((D5-C5)/C5,0)</f>
         <v>-0.779349593495935</v>
       </c>
-      <c r="G5" s="33" t="str">
+      <c r="G5" s="39" t="str">
         <f aca="false">IF(C5=0,"UNBUDGETED",IF(F5&gt;0.5,"CRITICAL",IF(F5&gt;0.1,"OVER",IF(F5&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>24600</v>
@@ -6021,21 +6213,21 @@
         <f aca="false">C6-D6</f>
         <v>9365</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="36" t="n">
         <f aca="false">IFERROR((D6-C6)/C6,0)</f>
         <v>-0.380691056910569</v>
       </c>
-      <c r="G6" s="33" t="str">
+      <c r="G6" s="39" t="str">
         <f aca="false">IF(C6=0,"UNBUDGETED",IF(F6&gt;0.5,"CRITICAL",IF(F6&gt;0.1,"OVER",IF(F6&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>0</v>
@@ -6047,21 +6239,21 @@
         <f aca="false">C7-D7</f>
         <v>-14.25</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="36" t="n">
         <f aca="false">IFERROR((D7-C7)/C7,0)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="33" t="str">
+      <c r="G7" s="39" t="str">
         <f aca="false">IF(C7=0,"UNBUDGETED",IF(F7&gt;0.5,"CRITICAL",IF(F7&gt;0.1,"OVER",IF(F7&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>675</v>
@@ -6073,21 +6265,21 @@
         <f aca="false">C8-D8</f>
         <v>5</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="36" t="n">
         <f aca="false">IFERROR((D8-C8)/C8,0)</f>
         <v>-0.00740740740740741</v>
       </c>
-      <c r="G8" s="33" t="str">
+      <c r="G8" s="39" t="str">
         <f aca="false">IF(C8=0,"UNBUDGETED",IF(F8&gt;0.5,"CRITICAL",IF(F8&gt;0.1,"OVER",IF(F8&lt;-0.1,"UNDER","ON"))))</f>
         <v>ON</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>96801</v>
@@ -6099,21 +6291,21 @@
         <f aca="false">C9-D9</f>
         <v>41340.75</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="36" t="n">
         <f aca="false">IFERROR((D9-C9)/C9,0)</f>
         <v>-0.427069451761862</v>
       </c>
-      <c r="G9" s="33" t="str">
+      <c r="G9" s="39" t="str">
         <f aca="false">IF(C9=0,"UNBUDGETED",IF(F9&gt;0.5,"CRITICAL",IF(F9&gt;0.1,"OVER",IF(F9&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>454876</v>
@@ -6125,21 +6317,21 @@
         <f aca="false">C10-D10</f>
         <v>-9522.31</v>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="36" t="n">
         <f aca="false">IFERROR((D10-C10)/C10,0)</f>
         <v>0.0209338588978095</v>
       </c>
-      <c r="G10" s="33" t="str">
+      <c r="G10" s="39" t="str">
         <f aca="false">IF(C10=0,"UNBUDGETED",IF(F10&gt;0.5,"CRITICAL",IF(F10&gt;0.1,"OVER",IF(F10&lt;-0.1,"UNDER","ON"))))</f>
         <v>ON</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>838640</v>
@@ -6151,21 +6343,21 @@
         <f aca="false">C11-D11</f>
         <v>216829.83</v>
       </c>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="36" t="n">
         <f aca="false">IFERROR((D11-C11)/C11,0)</f>
         <v>-0.258549353715539</v>
       </c>
-      <c r="G11" s="33" t="str">
+      <c r="G11" s="39" t="str">
         <f aca="false">IF(C11=0,"UNBUDGETED",IF(F11&gt;0.5,"CRITICAL",IF(F11&gt;0.1,"OVER",IF(F11&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
@@ -6177,21 +6369,21 @@
         <f aca="false">C12-D12</f>
         <v>-2568.72</v>
       </c>
-      <c r="F12" s="30" t="n">
+      <c r="F12" s="36" t="n">
         <f aca="false">IFERROR((D12-C12)/C12,0)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="33" t="str">
+      <c r="G12" s="39" t="str">
         <f aca="false">IF(C12=0,"UNBUDGETED",IF(F12&gt;0.5,"CRITICAL",IF(F12&gt;0.1,"OVER",IF(F12&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>26000</v>
@@ -6203,21 +6395,21 @@
         <f aca="false">C13-D13</f>
         <v>23590.12</v>
       </c>
-      <c r="F13" s="30" t="n">
+      <c r="F13" s="36" t="n">
         <f aca="false">IFERROR((D13-C13)/C13,0)</f>
         <v>-0.907312307692308</v>
       </c>
-      <c r="G13" s="33" t="str">
+      <c r="G13" s="39" t="str">
         <f aca="false">IF(C13=0,"UNBUDGETED",IF(F13&gt;0.5,"CRITICAL",IF(F13&gt;0.1,"OVER",IF(F13&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>5850</v>
@@ -6229,21 +6421,21 @@
         <f aca="false">C14-D14</f>
         <v>-16470</v>
       </c>
-      <c r="F14" s="30" t="n">
+      <c r="F14" s="36" t="n">
         <f aca="false">IFERROR((D14-C14)/C14,0)</f>
         <v>2.81538461538462</v>
       </c>
-      <c r="G14" s="33" t="str">
+      <c r="G14" s="39" t="str">
         <f aca="false">IF(C14=0,"UNBUDGETED",IF(F14&gt;0.5,"CRITICAL",IF(F14&gt;0.1,"OVER",IF(F14&lt;-0.1,"UNDER","ON"))))</f>
         <v>CRITICAL</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>0</v>
@@ -6255,21 +6447,21 @@
         <f aca="false">C15-D15</f>
         <v>-2472.45</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="36" t="n">
         <f aca="false">IFERROR((D15-C15)/C15,0)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="33" t="str">
+      <c r="G15" s="39" t="str">
         <f aca="false">IF(C15=0,"UNBUDGETED",IF(F15&gt;0.5,"CRITICAL",IF(F15&gt;0.1,"OVER",IF(F15&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>102758</v>
@@ -6281,21 +6473,21 @@
         <f aca="false">C16-D16</f>
         <v>63450.1</v>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="36" t="n">
         <f aca="false">IFERROR((D16-C16)/C16,0)</f>
         <v>-0.617471145798867</v>
       </c>
-      <c r="G16" s="33" t="str">
+      <c r="G16" s="39" t="str">
         <f aca="false">IF(C16=0,"UNBUDGETED",IF(F16&gt;0.5,"CRITICAL",IF(F16&gt;0.1,"OVER",IF(F16&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>12450</v>
@@ -6307,21 +6499,21 @@
         <f aca="false">C17-D17</f>
         <v>6935</v>
       </c>
-      <c r="F17" s="30" t="n">
+      <c r="F17" s="36" t="n">
         <f aca="false">IFERROR((D17-C17)/C17,0)</f>
         <v>-0.557028112449799</v>
       </c>
-      <c r="G17" s="33" t="str">
+      <c r="G17" s="39" t="str">
         <f aca="false">IF(C17=0,"UNBUDGETED",IF(F17&gt;0.5,"CRITICAL",IF(F17&gt;0.1,"OVER",IF(F17&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>448466.07</v>
@@ -6333,21 +6525,21 @@
         <f aca="false">C18-D18</f>
         <v>19725.66</v>
       </c>
-      <c r="F18" s="30" t="n">
+      <c r="F18" s="36" t="n">
         <f aca="false">IFERROR((D18-C18)/C18,0)</f>
         <v>-0.043984732222886</v>
       </c>
-      <c r="G18" s="33" t="str">
+      <c r="G18" s="39" t="str">
         <f aca="false">IF(C18=0,"UNBUDGETED",IF(F18&gt;0.5,"CRITICAL",IF(F18&gt;0.1,"OVER",IF(F18&lt;-0.1,"UNDER","ON"))))</f>
         <v>ON</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>90401.29</v>
@@ -6359,11 +6551,11 @@
         <f aca="false">C19-D19</f>
         <v>16501.44</v>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="36" t="n">
         <f aca="false">IFERROR((D19-C19)/C19,0)</f>
         <v>-0.182535448332651</v>
       </c>
-      <c r="G19" s="33" t="str">
+      <c r="G19" s="39" t="str">
         <f aca="false">IF(C19=0,"UNBUDGETED",IF(F19&gt;0.5,"CRITICAL",IF(F19&gt;0.1,"OVER",IF(F19&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNDER</v>
       </c>
@@ -6395,26 +6587,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>243</v>
+      <c r="A3" s="35" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>500869.06</v>
@@ -6422,14 +6614,14 @@
       <c r="C4" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D4" s="30" t="n">
+      <c r="D4" s="36" t="n">
         <f aca="false">IFERROR(B4/SUM(B$4:B$16),0)</f>
         <v>0.467237248122204</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>305149.79</v>
@@ -6437,14 +6629,14 @@
       <c r="C5" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="36" t="n">
         <f aca="false">IFERROR(B5/SUM(B$4:B$16),0)</f>
         <v>0.284659923183653</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>103987.31</v>
@@ -6452,14 +6644,14 @@
       <c r="C6" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="36" t="n">
         <f aca="false">IFERROR(B6/SUM(B$4:B$16),0)</f>
         <v>0.0970048830008197</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>76546</v>
@@ -6467,14 +6659,14 @@
       <c r="C7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="36" t="n">
         <f aca="false">IFERROR(B7/SUM(B$4:B$16),0)</f>
         <v>0.071406172293338</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>52035.97</v>
@@ -6482,14 +6674,14 @@
       <c r="C8" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="36" t="n">
         <f aca="false">IFERROR(B8/SUM(B$4:B$16),0)</f>
         <v>0.0485419151787287</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>22320</v>
@@ -6497,14 +6689,14 @@
       <c r="C9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="36" t="n">
         <f aca="false">IFERROR(B9/SUM(B$4:B$16),0)</f>
         <v>0.0208212808714669</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>2472.45</v>
@@ -6512,14 +6704,14 @@
       <c r="C10" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="36" t="n">
         <f aca="false">IFERROR(B10/SUM(B$4:B$16),0)</f>
         <v>0.00230643261158863</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>2408</v>
@@ -6527,14 +6719,14 @@
       <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="36" t="n">
         <f aca="false">IFERROR(B11/SUM(B$4:B$16),0)</f>
         <v>0.00224631023021919</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="B12" s="6" t="n">
         <v>1983.84</v>
@@ -6542,14 +6734,14 @@
       <c r="C12" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="30" t="n">
+      <c r="D12" s="36" t="n">
         <f aca="false">IFERROR(B12/SUM(B$4:B$16),0)</f>
         <v>0.00185063126541446</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="B13" s="6" t="n">
         <v>1865.27</v>
@@ -6557,14 +6749,14 @@
       <c r="C13" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="36" t="n">
         <f aca="false">IFERROR(B13/SUM(B$4:B$16),0)</f>
         <v>0.00174002287505023</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>1602.9</v>
@@ -6572,14 +6764,14 @@
       <c r="C14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="30" t="n">
+      <c r="D14" s="36" t="n">
         <f aca="false">IFERROR(B14/SUM(B$4:B$16),0)</f>
         <v>0.00149527021097107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="B15" s="6" t="n">
         <v>544.61</v>
@@ -6587,14 +6779,14 @@
       <c r="C15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="30" t="n">
+      <c r="D15" s="36" t="n">
         <f aca="false">IFERROR(B15/SUM(B$4:B$16),0)</f>
         <v>0.000508041118969963</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="B16" s="6" t="n">
         <v>194.96</v>
@@ -6602,20 +6794,20 @@
       <c r="C16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="30" t="n">
+      <c r="D16" s="36" t="n">
         <f aca="false">IFERROR(B16/SUM(B$4:B$16),0)</f>
         <v>0.000181869037576218</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="B17" s="7" t="n">
         <f aca="false">SUM(B4:B16)</f>
         <v>1071980.16</v>
       </c>
-      <c r="C17" s="34" t="n">
+      <c r="C17" s="40" t="n">
         <f aca="false">SUM(C4:C16)</f>
         <v>436</v>
       </c>
